--- a/optimized_version/metadata/testing_daily_metrics/agus6_testing_daily_metrics.xlsx
+++ b/optimized_version/metadata/testing_daily_metrics/agus6_testing_daily_metrics.xlsx
@@ -467,7 +467,7 @@
         <v>45757</v>
       </c>
       <c r="B2" t="n">
-        <v>2.553979018669717</v>
+        <v>2.549593713028371</v>
       </c>
       <c r="C2" t="n">
         <v>1</v>
@@ -476,10 +476,10 @@
         <v>0</v>
       </c>
       <c r="E2" t="n">
-        <v>4.057016102988996</v>
+        <v>4.050050009895273</v>
       </c>
       <c r="F2" t="n">
-        <v>4.057016102988996</v>
+        <v>4.050050009895273</v>
       </c>
       <c r="G2" t="inlineStr"/>
       <c r="H2" t="n">
@@ -491,7 +491,7 @@
         <v>45758</v>
       </c>
       <c r="B3" t="n">
-        <v>0.8502867760926276</v>
+        <v>0.8499060895308863</v>
       </c>
       <c r="C3" t="n">
         <v>24</v>
@@ -500,13 +500,13 @@
         <v>0</v>
       </c>
       <c r="E3" t="n">
-        <v>1.319243008582422</v>
+        <v>1.318662500824611</v>
       </c>
       <c r="F3" t="n">
-        <v>2.96074717349056</v>
+        <v>2.960782005416208</v>
       </c>
       <c r="G3" t="n">
-        <v>-0.4782060591916815</v>
+        <v>-0.4782408403218494</v>
       </c>
       <c r="H3" t="n">
         <v>24</v>
@@ -517,7 +517,7 @@
         <v>45759</v>
       </c>
       <c r="B4" t="n">
-        <v>0.8685836804652532</v>
+        <v>0.8678273405686965</v>
       </c>
       <c r="C4" t="n">
         <v>24</v>
@@ -526,13 +526,13 @@
         <v>0</v>
       </c>
       <c r="E4" t="n">
-        <v>1.362481850498166</v>
+        <v>1.361320834982547</v>
       </c>
       <c r="F4" t="n">
-        <v>2.460520592050907</v>
+        <v>2.459727272199246</v>
       </c>
       <c r="G4" t="n">
-        <v>0.4377480011458634</v>
+        <v>0.438110504728929</v>
       </c>
       <c r="H4" t="n">
         <v>24</v>
@@ -543,7 +543,7 @@
         <v>45760</v>
       </c>
       <c r="B5" t="n">
-        <v>6.227603736128041</v>
+        <v>6.228736109019021</v>
       </c>
       <c r="C5" t="n">
         <v>24</v>
@@ -552,13 +552,13 @@
         <v>0</v>
       </c>
       <c r="E5" t="n">
-        <v>8.378479307586078</v>
+        <v>8.380220830859507</v>
       </c>
       <c r="F5" t="n">
-        <v>14.75658034312355</v>
+        <v>14.75736364273668</v>
       </c>
       <c r="G5" t="n">
-        <v>0.7973076140594305</v>
+        <v>0.7972860951061722</v>
       </c>
       <c r="H5" t="n">
         <v>24</v>
@@ -569,7 +569,7 @@
         <v>45761</v>
       </c>
       <c r="B6" t="n">
-        <v>2.325734028036769</v>
+        <v>2.325395562539609</v>
       </c>
       <c r="C6" t="n">
         <v>24</v>
@@ -578,13 +578,13 @@
         <v>0</v>
       </c>
       <c r="E6" t="n">
-        <v>4.050401341915753</v>
+        <v>4.049820834157941</v>
       </c>
       <c r="F6" t="n">
-        <v>5.957407150928085</v>
+        <v>5.956669549609707</v>
       </c>
       <c r="G6" t="n">
-        <v>0.4218308528904023</v>
+        <v>0.421974013132407</v>
       </c>
       <c r="H6" t="n">
         <v>24</v>
@@ -595,7 +595,7 @@
         <v>45762</v>
       </c>
       <c r="B7" t="n">
-        <v>0.7400411771708099</v>
+        <v>0.7393897584218099</v>
       </c>
       <c r="C7" t="n">
         <v>24</v>
@@ -604,13 +604,13 @@
         <v>0</v>
       </c>
       <c r="E7" t="n">
-        <v>1.315486017164832</v>
+        <v>1.314325001649211</v>
       </c>
       <c r="F7" t="n">
-        <v>2.117914105767706</v>
+        <v>2.118143456201913</v>
       </c>
       <c r="G7" t="n">
-        <v>0.624875599919547</v>
+        <v>0.6247943505410205</v>
       </c>
       <c r="H7" t="n">
         <v>24</v>
@@ -621,7 +621,7 @@
         <v>45763</v>
       </c>
       <c r="B8" t="n">
-        <v>2.455525437802466</v>
+        <v>2.456302627248769</v>
       </c>
       <c r="C8" t="n">
         <v>24</v>
@@ -630,13 +630,13 @@
         <v>0</v>
       </c>
       <c r="E8" t="n">
-        <v>4.308213982835166</v>
+        <v>4.309587497526177</v>
       </c>
       <c r="F8" t="n">
-        <v>6.841714148079744</v>
+        <v>6.841717512595611</v>
       </c>
       <c r="G8" t="n">
-        <v>0.06417174453038488</v>
+        <v>0.0641708241149096</v>
       </c>
       <c r="H8" t="n">
         <v>24</v>
@@ -647,7 +647,7 @@
         <v>45764</v>
       </c>
       <c r="B9" t="n">
-        <v>11.7903093366189</v>
+        <v>11.7897559045285</v>
       </c>
       <c r="C9" t="n">
         <v>24</v>
@@ -656,13 +656,13 @@
         <v>0</v>
       </c>
       <c r="E9" t="n">
-        <v>14.03850967524908</v>
+        <v>14.03792916749128</v>
       </c>
       <c r="F9" t="n">
-        <v>21.46506439232911</v>
+        <v>21.46410990193405</v>
       </c>
       <c r="G9" t="n">
-        <v>0.4625530496856856</v>
+        <v>0.4626008460991505</v>
       </c>
       <c r="H9" t="n">
         <v>24</v>
@@ -673,7 +673,7 @@
         <v>45765</v>
       </c>
       <c r="B10" t="n">
-        <v>4.541754085424741</v>
+        <v>4.543894053567266</v>
       </c>
       <c r="C10" t="n">
         <v>24</v>
@@ -682,13 +682,13 @@
         <v>0</v>
       </c>
       <c r="E10" t="n">
-        <v>4.65007514091941</v>
+        <v>4.652295830034894</v>
       </c>
       <c r="F10" t="n">
-        <v>7.396997991949481</v>
+        <v>7.396939364366955</v>
       </c>
       <c r="G10" t="n">
-        <v>0.5320950894894008</v>
+        <v>0.5321025065591561</v>
       </c>
       <c r="H10" t="n">
         <v>24</v>
@@ -699,7 +699,7 @@
         <v>45766</v>
       </c>
       <c r="B11" t="n">
-        <v>5.00588866129581</v>
+        <v>5.005756000996196</v>
       </c>
       <c r="C11" t="n">
         <v>24</v>
@@ -708,13 +708,13 @@
         <v>0</v>
       </c>
       <c r="E11" t="n">
-        <v>5.452874999999999</v>
+        <v>5.452875</v>
       </c>
       <c r="F11" t="n">
-        <v>8.425774979413086</v>
+        <v>8.425751444509929</v>
       </c>
       <c r="G11" t="n">
-        <v>0.1164545175208965</v>
+        <v>0.1164594533584603</v>
       </c>
       <c r="H11" t="n">
         <v>24</v>
@@ -725,7 +725,7 @@
         <v>45767</v>
       </c>
       <c r="B12" t="n">
-        <v>1.7388253578716</v>
+        <v>1.741731300093242</v>
       </c>
       <c r="C12" t="n">
         <v>24</v>
@@ -734,13 +734,13 @@
         <v>0</v>
       </c>
       <c r="E12" t="n">
-        <v>2.468271115172156</v>
+        <v>2.471754161719014</v>
       </c>
       <c r="F12" t="n">
-        <v>7.022647457577882</v>
+        <v>7.024863807626811</v>
       </c>
       <c r="G12" t="n">
-        <v>0.9210203793061288</v>
+        <v>0.9209705194464067</v>
       </c>
       <c r="H12" t="n">
         <v>24</v>
@@ -751,7 +751,7 @@
         <v>45768</v>
       </c>
       <c r="B13" t="n">
-        <v>0.2548525683748545</v>
+        <v>0.2552101402589769</v>
       </c>
       <c r="C13" t="n">
         <v>24</v>
@@ -760,13 +760,13 @@
         <v>0</v>
       </c>
       <c r="E13" t="n">
-        <v>0.4072611580842462</v>
+        <v>0.4078416658420565</v>
       </c>
       <c r="F13" t="n">
-        <v>0.4768190597948315</v>
+        <v>0.4771787482453187</v>
       </c>
       <c r="G13" t="n">
-        <v>-0.3084629545171267</v>
+        <v>-0.3104377771095741</v>
       </c>
       <c r="H13" t="n">
         <v>24</v>
@@ -777,7 +777,7 @@
         <v>45769</v>
       </c>
       <c r="B14" t="n">
-        <v>0.7737718665140005</v>
+        <v>0.7741169417354196</v>
       </c>
       <c r="C14" t="n">
         <v>24</v>
@@ -786,13 +786,13 @@
         <v>0</v>
       </c>
       <c r="E14" t="n">
-        <v>1.218494491417577</v>
+        <v>1.219074999175387</v>
       </c>
       <c r="F14" t="n">
-        <v>2.288368166509222</v>
+        <v>2.288378225647079</v>
       </c>
       <c r="G14" t="n">
-        <v>-0.8820587055390621</v>
+        <v>-0.8820752517660728</v>
       </c>
       <c r="H14" t="n">
         <v>24</v>
@@ -803,7 +803,7 @@
         <v>45770</v>
       </c>
       <c r="B15" t="n">
-        <v>0.2577936656963984</v>
+        <v>0.2574270715459003</v>
       </c>
       <c r="C15" t="n">
         <v>24</v>
@@ -812,13 +812,13 @@
         <v>0</v>
       </c>
       <c r="E15" t="n">
-        <v>0.4119305085824235</v>
+        <v>0.411350000824618</v>
       </c>
       <c r="F15" t="n">
-        <v>0.5048684619796311</v>
+        <v>0.5051511848203936</v>
       </c>
       <c r="G15" t="n">
-        <v>-0.451066102557139</v>
+        <v>-0.4526917315278509</v>
       </c>
       <c r="H15" t="n">
         <v>24</v>
@@ -829,7 +829,7 @@
         <v>45771</v>
       </c>
       <c r="B16" t="n">
-        <v>1.196792115930799</v>
+        <v>1.196374832436242</v>
       </c>
       <c r="C16" t="n">
         <v>24</v>
@@ -838,13 +838,13 @@
         <v>0</v>
       </c>
       <c r="E16" t="n">
-        <v>1.793155508582417</v>
+        <v>1.792575000824609</v>
       </c>
       <c r="F16" t="n">
-        <v>5.138650377154987</v>
+        <v>5.138669825092268</v>
       </c>
       <c r="G16" t="n">
-        <v>0.4419219985903924</v>
+        <v>0.4419177743347179</v>
       </c>
       <c r="H16" t="n">
         <v>24</v>
@@ -855,7 +855,7 @@
         <v>45772</v>
       </c>
       <c r="B17" t="n">
-        <v>0.2589020282665796</v>
+        <v>0.2592593750661586</v>
       </c>
       <c r="C17" t="n">
         <v>24</v>
@@ -864,13 +864,13 @@
         <v>0</v>
       </c>
       <c r="E17" t="n">
-        <v>0.4142153247509093</v>
+        <v>0.414795832508716</v>
       </c>
       <c r="F17" t="n">
-        <v>0.5081973840055416</v>
+        <v>0.5078532141224184</v>
       </c>
       <c r="G17" t="n">
-        <v>-0.3982903253356398</v>
+        <v>-0.3963970198086237</v>
       </c>
       <c r="H17" t="n">
         <v>24</v>
@@ -881,7 +881,7 @@
         <v>45773</v>
       </c>
       <c r="B18" t="n">
-        <v>0.6976315397648812</v>
+        <v>0.6977935288212251</v>
       </c>
       <c r="C18" t="n">
         <v>24</v>
@@ -890,13 +890,13 @@
         <v>0</v>
       </c>
       <c r="E18" t="n">
-        <v>1.062325000000006</v>
+        <v>1.062587499175397</v>
       </c>
       <c r="F18" t="n">
-        <v>2.331120747748772</v>
+        <v>2.33103256709305</v>
       </c>
       <c r="G18" t="n">
-        <v>0.7523428135065345</v>
+        <v>0.7523615496960434</v>
       </c>
       <c r="H18" t="n">
         <v>24</v>
@@ -907,7 +907,7 @@
         <v>45774</v>
       </c>
       <c r="B19" t="n">
-        <v>4.269461536475409</v>
+        <v>4.268978695760897</v>
       </c>
       <c r="C19" t="n">
         <v>24</v>
@@ -916,13 +916,13 @@
         <v>0</v>
       </c>
       <c r="E19" t="n">
-        <v>5.474501341915752</v>
+        <v>5.47392083415794</v>
       </c>
       <c r="F19" t="n">
-        <v>11.23160394517526</v>
+        <v>11.23101033024361</v>
       </c>
       <c r="G19" t="n">
-        <v>0.5623481600659463</v>
+        <v>0.5623944205649635</v>
       </c>
       <c r="H19" t="n">
         <v>24</v>
@@ -933,7 +933,7 @@
         <v>45775</v>
       </c>
       <c r="B20" t="n">
-        <v>0.9937001231759282</v>
+        <v>0.9937890303145369</v>
       </c>
       <c r="C20" t="n">
         <v>24</v>
@@ -942,13 +942,13 @@
         <v>0</v>
       </c>
       <c r="E20" t="n">
-        <v>1.512770833333341</v>
+        <v>1.512966665842061</v>
       </c>
       <c r="F20" t="n">
-        <v>3.517969018382851</v>
+        <v>3.519929172393698</v>
       </c>
       <c r="G20" t="n">
-        <v>0.8162802151965454</v>
+        <v>0.8160754269239024</v>
       </c>
       <c r="H20" t="n">
         <v>24</v>
@@ -959,7 +959,7 @@
         <v>45776</v>
       </c>
       <c r="B21" t="n">
-        <v>0.1693255722592796</v>
+        <v>0.1693222584874468</v>
       </c>
       <c r="C21" t="n">
         <v>24</v>
@@ -968,13 +968,13 @@
         <v>0</v>
       </c>
       <c r="E21" t="n">
-        <v>0.2699916666666684</v>
+        <v>0.2699916666666695</v>
       </c>
       <c r="F21" t="n">
-        <v>0.3297895459909138</v>
+        <v>0.3296899073742</v>
       </c>
       <c r="G21" t="n">
-        <v>-0.7597447287398631</v>
+        <v>-0.7586815534795022</v>
       </c>
       <c r="H21" t="n">
         <v>24</v>
@@ -985,7 +985,7 @@
         <v>45777</v>
       </c>
       <c r="B22" t="n">
-        <v>0.2391080987513867</v>
+        <v>0.2391032300795721</v>
       </c>
       <c r="C22" t="n">
         <v>24</v>
@@ -994,13 +994,13 @@
         <v>0</v>
       </c>
       <c r="E22" t="n">
-        <v>0.379641666666662</v>
+        <v>0.3796416666666609</v>
       </c>
       <c r="F22" t="n">
-        <v>0.6515272525435778</v>
+        <v>0.6515774166115732</v>
       </c>
       <c r="G22" t="n">
-        <v>-0.9754869272664071</v>
+        <v>-0.9757911425549577</v>
       </c>
       <c r="H22" t="n">
         <v>24</v>
@@ -1011,7 +1011,7 @@
         <v>45778</v>
       </c>
       <c r="B23" t="n">
-        <v>1.583308045423243</v>
+        <v>1.584378996469918</v>
       </c>
       <c r="C23" t="n">
         <v>24</v>
@@ -1020,13 +1020,13 @@
         <v>0</v>
       </c>
       <c r="E23" t="n">
-        <v>2.338905649501831</v>
+        <v>2.340479164192843</v>
       </c>
       <c r="F23" t="n">
-        <v>6.067653312766471</v>
+        <v>6.067672342321204</v>
       </c>
       <c r="G23" t="n">
-        <v>0.6880354210366171</v>
+        <v>0.6880334642483719</v>
       </c>
       <c r="H23" t="n">
         <v>24</v>
@@ -1037,7 +1037,7 @@
         <v>45779</v>
       </c>
       <c r="B24" t="n">
-        <v>0.3062615868414418</v>
+        <v>0.3058898578795372</v>
       </c>
       <c r="C24" t="n">
         <v>24</v>
@@ -1046,13 +1046,13 @@
         <v>0</v>
       </c>
       <c r="E24" t="n">
-        <v>0.4853305085824135</v>
+        <v>0.484750000824602</v>
       </c>
       <c r="F24" t="n">
-        <v>0.7784167556341057</v>
+        <v>0.7780258473397055</v>
       </c>
       <c r="G24" t="n">
-        <v>-1.257726061694112</v>
+        <v>-1.255459044102378</v>
       </c>
       <c r="H24" t="n">
         <v>24</v>
@@ -1063,7 +1063,7 @@
         <v>45780</v>
       </c>
       <c r="B25" t="n">
-        <v>0.1027290837989674</v>
+        <v>0.1031682285552962</v>
       </c>
       <c r="C25" t="n">
         <v>24</v>
@@ -1072,13 +1072,13 @@
         <v>0</v>
       </c>
       <c r="E25" t="n">
-        <v>0.1629499999999986</v>
+        <v>0.1636499983507823</v>
       </c>
       <c r="F25" t="n">
-        <v>0.2314913178235434</v>
+        <v>0.2322904006582356</v>
       </c>
       <c r="G25" t="n">
-        <v>-0.09074693404381051</v>
+        <v>-0.09829021030531737</v>
       </c>
       <c r="H25" t="n">
         <v>24</v>
@@ -1089,7 +1089,7 @@
         <v>45781</v>
       </c>
       <c r="B26" t="n">
-        <v>0.2383464031304588</v>
+        <v>0.2379749977461462</v>
       </c>
       <c r="C26" t="n">
         <v>24</v>
@@ -1098,13 +1098,13 @@
         <v>0</v>
       </c>
       <c r="E26" t="n">
-        <v>0.3777888419157544</v>
+        <v>0.3772083341579512</v>
       </c>
       <c r="F26" t="n">
-        <v>0.5026534649900382</v>
+        <v>0.5016425616976303</v>
       </c>
       <c r="G26" t="n">
-        <v>-0.5072002784410967</v>
+        <v>-0.5011440121889335</v>
       </c>
       <c r="H26" t="n">
         <v>24</v>
@@ -1115,7 +1115,7 @@
         <v>45782</v>
       </c>
       <c r="B27" t="n">
-        <v>0.2260287923208242</v>
+        <v>0.2263283616096268</v>
       </c>
       <c r="C27" t="n">
         <v>24</v>
@@ -1124,13 +1124,13 @@
         <v>0</v>
       </c>
       <c r="E27" t="n">
-        <v>0.3585125000000033</v>
+        <v>0.3589916658420632</v>
       </c>
       <c r="F27" t="n">
-        <v>0.5410765515769808</v>
+        <v>0.5419092168206023</v>
       </c>
       <c r="G27" t="n">
-        <v>-2.668905338054842</v>
+        <v>-2.680206218131883</v>
       </c>
       <c r="H27" t="n">
         <v>24</v>
@@ -1141,7 +1141,7 @@
         <v>45783</v>
       </c>
       <c r="B28" t="n">
-        <v>0.4564277087278403</v>
+        <v>0.4567828384538801</v>
       </c>
       <c r="C28" t="n">
         <v>24</v>
@@ -1150,13 +1150,13 @@
         <v>0</v>
       </c>
       <c r="E28" t="n">
-        <v>0.7178986580842471</v>
+        <v>0.7184791658420527</v>
       </c>
       <c r="F28" t="n">
-        <v>1.680300652157381</v>
+        <v>1.680365049264694</v>
       </c>
       <c r="G28" t="n">
-        <v>-1.002895750062923</v>
+        <v>-1.003049273974213</v>
       </c>
       <c r="H28" t="n">
         <v>24</v>
@@ -1167,7 +1167,7 @@
         <v>45784</v>
       </c>
       <c r="B29" t="n">
-        <v>0.5055125081638526</v>
+        <v>0.5051346814479134</v>
       </c>
       <c r="C29" t="n">
         <v>24</v>
@@ -1176,13 +1176,13 @@
         <v>0</v>
       </c>
       <c r="E29" t="n">
-        <v>0.7947430085824152</v>
+        <v>0.7941625008246085</v>
       </c>
       <c r="F29" t="n">
-        <v>1.633789306632976</v>
+        <v>1.633939136739462</v>
       </c>
       <c r="G29" t="n">
-        <v>-1.046929102034115</v>
+        <v>-1.04730455518096</v>
       </c>
       <c r="H29" t="n">
         <v>24</v>
@@ -1193,7 +1193,7 @@
         <v>45785</v>
       </c>
       <c r="B30" t="n">
-        <v>0.2180989039868231</v>
+        <v>0.2177308444845783</v>
       </c>
       <c r="C30" t="n">
         <v>24</v>
@@ -1202,13 +1202,13 @@
         <v>0</v>
       </c>
       <c r="E30" t="n">
-        <v>0.3464305085824163</v>
+        <v>0.3458500008246048</v>
       </c>
       <c r="F30" t="n">
-        <v>0.4085570119539815</v>
+        <v>0.4078312293168171</v>
       </c>
       <c r="G30" t="n">
-        <v>-0.3471942994538264</v>
+        <v>-0.34241209417501</v>
       </c>
       <c r="H30" t="n">
         <v>24</v>
@@ -1219,7 +1219,7 @@
         <v>45786</v>
       </c>
       <c r="B31" t="n">
-        <v>0.1505520022441492</v>
+        <v>0.1509142014691166</v>
       </c>
       <c r="C31" t="n">
         <v>24</v>
@@ -1228,13 +1228,13 @@
         <v>0</v>
       </c>
       <c r="E31" t="n">
-        <v>0.2396653247509128</v>
+        <v>0.2402458325087219</v>
       </c>
       <c r="F31" t="n">
-        <v>0.3199620987091568</v>
+        <v>0.3207429345344142</v>
       </c>
       <c r="G31" t="n">
-        <v>0.5843092140738609</v>
+        <v>0.5822778339853716</v>
       </c>
       <c r="H31" t="n">
         <v>24</v>
@@ -1245,7 +1245,7 @@
         <v>45787</v>
       </c>
       <c r="B32" t="n">
-        <v>0.135812658517762</v>
+        <v>0.1354434588238334</v>
       </c>
       <c r="C32" t="n">
         <v>24</v>
@@ -1254,13 +1254,13 @@
         <v>0</v>
       </c>
       <c r="E32" t="n">
-        <v>0.2156805085824208</v>
+        <v>0.2151000008246129</v>
       </c>
       <c r="F32" t="n">
-        <v>0.2796946647655371</v>
+        <v>0.2789753104403208</v>
       </c>
       <c r="G32" t="n">
-        <v>0.4859347595710521</v>
+        <v>0.4885756359100439</v>
       </c>
       <c r="H32" t="n">
         <v>24</v>
@@ -1271,7 +1271,7 @@
         <v>45788</v>
       </c>
       <c r="B33" t="n">
-        <v>0.2589069129836397</v>
+        <v>0.2581700491521485</v>
       </c>
       <c r="C33" t="n">
         <v>24</v>
@@ -1280,13 +1280,13 @@
         <v>0</v>
       </c>
       <c r="E33" t="n">
-        <v>0.4099735171648315</v>
+        <v>0.4088125016492133</v>
       </c>
       <c r="F33" t="n">
-        <v>0.5344637918109982</v>
+        <v>0.5344068238251573</v>
       </c>
       <c r="G33" t="n">
-        <v>-0.4118537383578675</v>
+        <v>-0.4115527781113353</v>
       </c>
       <c r="H33" t="n">
         <v>24</v>
@@ -1297,7 +1297,7 @@
         <v>45789</v>
       </c>
       <c r="B34" t="n">
-        <v>5.651051195439867</v>
+        <v>5.650626198054603</v>
       </c>
       <c r="C34" t="n">
         <v>24</v>
@@ -1306,13 +1306,13 @@
         <v>0</v>
       </c>
       <c r="E34" t="n">
-        <v>6.558151341915749</v>
+        <v>6.557570834157938</v>
       </c>
       <c r="F34" t="n">
-        <v>18.04407278990192</v>
+        <v>18.04408471282172</v>
       </c>
       <c r="G34" t="n">
-        <v>0.5744197129336772</v>
+        <v>0.5744191505150515</v>
       </c>
       <c r="H34" t="n">
         <v>24</v>
@@ -1323,7 +1323,7 @@
         <v>45790</v>
       </c>
       <c r="B35" t="n">
-        <v>0.30505576352911</v>
+        <v>0.3039538143032038</v>
       </c>
       <c r="C35" t="n">
         <v>24</v>
@@ -1332,13 +1332,13 @@
         <v>0</v>
       </c>
       <c r="E35" t="n">
-        <v>0.4838331924139171</v>
+        <v>0.4820916691404887</v>
       </c>
       <c r="F35" t="n">
-        <v>0.7842880135037098</v>
+        <v>0.7842735454737453</v>
       </c>
       <c r="G35" t="n">
-        <v>-1.054600637777561</v>
+        <v>-1.054524834631529</v>
       </c>
       <c r="H35" t="n">
         <v>24</v>
@@ -1349,7 +1349,7 @@
         <v>45791</v>
       </c>
       <c r="B36" t="n">
-        <v>0.1525905968224907</v>
+        <v>0.1526977729451902</v>
       </c>
       <c r="C36" t="n">
         <v>24</v>
@@ -1358,13 +1358,13 @@
         <v>0</v>
       </c>
       <c r="E36" t="n">
-        <v>0.2423513333333318</v>
+        <v>0.2425278325087206</v>
       </c>
       <c r="F36" t="n">
-        <v>0.3299638886955169</v>
+        <v>0.3298493156191968</v>
       </c>
       <c r="G36" t="n">
-        <v>0.03936073600854906</v>
+        <v>0.04002774407137344</v>
       </c>
       <c r="H36" t="n">
         <v>24</v>
@@ -1375,7 +1375,7 @@
         <v>45792</v>
       </c>
       <c r="B37" t="n">
-        <v>0.003053642076793989</v>
+        <v>0.001334044205862042</v>
       </c>
       <c r="C37" t="n">
         <v>24</v>
@@ -1384,13 +1384,13 @@
         <v>0</v>
       </c>
       <c r="E37" t="n">
-        <v>0.00484810298901787</v>
+        <v>0.002117990104692306</v>
       </c>
       <c r="F37" t="n">
-        <v>0.00484810298901787</v>
+        <v>0.002117990104692306</v>
       </c>
       <c r="G37" t="n">
-        <v>0.9761176382128675</v>
+        <v>0.9954419251518141</v>
       </c>
       <c r="H37" t="n">
         <v>24</v>
@@ -1401,7 +1401,7 @@
         <v>45793</v>
       </c>
       <c r="B38" t="n">
-        <v>3.310491949715452</v>
+        <v>3.309217197753584</v>
       </c>
       <c r="C38" t="n">
         <v>24</v>
@@ -1410,13 +1410,13 @@
         <v>0</v>
       </c>
       <c r="E38" t="n">
-        <v>4.350945692413919</v>
+        <v>4.349204169140489</v>
       </c>
       <c r="F38" t="n">
-        <v>10.4678988520216</v>
+        <v>10.4678923416699</v>
       </c>
       <c r="G38" t="n">
-        <v>0.7961631386766799</v>
+        <v>0.7961633922231199</v>
       </c>
       <c r="H38" t="n">
         <v>24</v>
@@ -1427,7 +1427,7 @@
         <v>45794</v>
       </c>
       <c r="B39" t="n">
-        <v>1.289532933196667</v>
+        <v>1.288493345868907</v>
       </c>
       <c r="C39" t="n">
         <v>24</v>
@@ -1436,13 +1436,13 @@
         <v>0</v>
       </c>
       <c r="E39" t="n">
-        <v>1.621681850498168</v>
+        <v>1.62052083498255</v>
       </c>
       <c r="F39" t="n">
-        <v>6.877868674536869</v>
+        <v>6.876455572279967</v>
       </c>
       <c r="G39" t="n">
-        <v>0.8153473069771311</v>
+        <v>0.8154231753440355</v>
       </c>
       <c r="H39" t="n">
         <v>24</v>
@@ -1453,7 +1453,7 @@
         <v>45795</v>
       </c>
       <c r="B40" t="n">
-        <v>0.1714109116512945</v>
+        <v>0.1718729429307247</v>
       </c>
       <c r="C40" t="n">
         <v>24</v>
@@ -1462,13 +1462,13 @@
         <v>0</v>
       </c>
       <c r="E40" t="n">
-        <v>0.2143153247509181</v>
+        <v>0.2148958325087271</v>
       </c>
       <c r="F40" t="n">
-        <v>0.2669646642109415</v>
+        <v>0.2676524414399322</v>
       </c>
       <c r="G40" t="n">
-        <v>-0.0001071234087126616</v>
+        <v>-0.005266884594868904</v>
       </c>
       <c r="H40" t="n">
         <v>24</v>
@@ -1479,7 +1479,7 @@
         <v>45796</v>
       </c>
       <c r="B41" t="n">
-        <v>1.145826822836614</v>
+        <v>1.145753084713907</v>
       </c>
       <c r="C41" t="n">
         <v>24</v>
@@ -1488,13 +1488,13 @@
         <v>0</v>
       </c>
       <c r="E41" t="n">
-        <v>1.678100000000001</v>
+        <v>1.6781</v>
       </c>
       <c r="F41" t="n">
-        <v>5.148790995614214</v>
+        <v>5.150699360314504</v>
       </c>
       <c r="G41" t="n">
-        <v>0.7926365944365051</v>
+        <v>0.7924828502507149</v>
       </c>
       <c r="H41" t="n">
         <v>24</v>
@@ -1505,7 +1505,7 @@
         <v>45797</v>
       </c>
       <c r="B42" t="n">
-        <v>0.4446517887086465</v>
+        <v>0.4450071692015216</v>
       </c>
       <c r="C42" t="n">
         <v>24</v>
@@ -1514,13 +1514,13 @@
         <v>0</v>
       </c>
       <c r="E42" t="n">
-        <v>0.7014194914175876</v>
+        <v>0.7019999991753991</v>
       </c>
       <c r="F42" t="n">
-        <v>1.202540735755616</v>
+        <v>1.202586813473488</v>
       </c>
       <c r="G42" t="n">
-        <v>-0.6679517227682494</v>
+        <v>-0.6680795469309631</v>
       </c>
       <c r="H42" t="n">
         <v>24</v>
@@ -1531,7 +1531,7 @@
         <v>45798</v>
       </c>
       <c r="B43" t="n">
-        <v>0.2369329355498859</v>
+        <v>0.2365633259707147</v>
       </c>
       <c r="C43" t="n">
         <v>24</v>
@@ -1540,13 +1540,13 @@
         <v>0</v>
       </c>
       <c r="E43" t="n">
-        <v>0.3768471752490872</v>
+        <v>0.3762666674912782</v>
       </c>
       <c r="F43" t="n">
-        <v>0.4676819582692652</v>
+        <v>0.4673877569233583</v>
       </c>
       <c r="G43" t="n">
-        <v>-0.9480783435736211</v>
+        <v>-0.9456281870347871</v>
       </c>
       <c r="H43" t="n">
         <v>24</v>
@@ -1557,7 +1557,7 @@
         <v>45799</v>
       </c>
       <c r="B44" t="n">
-        <v>0.1761352615863984</v>
+        <v>0.1764963820379925</v>
       </c>
       <c r="C44" t="n">
         <v>24</v>
@@ -1566,13 +1566,13 @@
         <v>0</v>
       </c>
       <c r="E44" t="n">
-        <v>0.2799569914175872</v>
+        <v>0.2805374991753951</v>
       </c>
       <c r="F44" t="n">
-        <v>0.3490759406761448</v>
+        <v>0.3498354363273879</v>
       </c>
       <c r="G44" t="n">
-        <v>-0.184945679463844</v>
+        <v>-0.1901075369426661</v>
       </c>
       <c r="H44" t="n">
         <v>24</v>
@@ -1583,7 +1583,7 @@
         <v>45800</v>
       </c>
       <c r="B45" t="n">
-        <v>0.8622430096101552</v>
+        <v>0.8629512491131369</v>
       </c>
       <c r="C45" t="n">
         <v>24</v>
@@ -1592,13 +1592,13 @@
         <v>0</v>
       </c>
       <c r="E45" t="n">
-        <v>1.358726482835169</v>
+        <v>1.359887498350792</v>
       </c>
       <c r="F45" t="n">
-        <v>2.415542172641456</v>
+        <v>2.415575037240385</v>
       </c>
       <c r="G45" t="n">
-        <v>-1.263841903731449</v>
+        <v>-1.263903505439897</v>
       </c>
       <c r="H45" t="n">
         <v>24</v>
@@ -1609,7 +1609,7 @@
         <v>45801</v>
       </c>
       <c r="B46" t="n">
-        <v>0.2113924182535786</v>
+        <v>0.2124823176918161</v>
       </c>
       <c r="C46" t="n">
         <v>24</v>
@@ -1618,13 +1618,13 @@
         <v>0</v>
       </c>
       <c r="E46" t="n">
-        <v>0.3367709742527438</v>
+        <v>0.3385124975261687</v>
       </c>
       <c r="F46" t="n">
-        <v>0.4373082039477028</v>
+        <v>0.4368084671911842</v>
       </c>
       <c r="G46" t="n">
-        <v>-0.1288465199527604</v>
+        <v>-0.1262680008943979</v>
       </c>
       <c r="H46" t="n">
         <v>24</v>
@@ -1635,7 +1635,7 @@
         <v>45802</v>
       </c>
       <c r="B47" t="n">
-        <v>5.701417067825202</v>
+        <v>5.702635964250892</v>
       </c>
       <c r="C47" t="n">
         <v>24</v>
@@ -1644,13 +1644,13 @@
         <v>0</v>
       </c>
       <c r="E47" t="n">
-        <v>6.599591807586073</v>
+        <v>6.601333330859501</v>
       </c>
       <c r="F47" t="n">
-        <v>13.195188037668</v>
+        <v>13.19519753829305</v>
       </c>
       <c r="G47" t="n">
-        <v>0.8142106338351</v>
+        <v>0.8142103662957914</v>
       </c>
       <c r="H47" t="n">
         <v>24</v>
@@ -1661,7 +1661,7 @@
         <v>45803</v>
       </c>
       <c r="B48" t="n">
-        <v>0.1597765756936674</v>
+        <v>0.1589435093828475</v>
       </c>
       <c r="C48" t="n">
         <v>24</v>
@@ -1670,13 +1670,13 @@
         <v>0</v>
       </c>
       <c r="E48" t="n">
-        <v>0.2542790257472577</v>
+        <v>0.2529583349825562</v>
       </c>
       <c r="F48" t="n">
-        <v>0.3148763147273319</v>
+        <v>0.31448910995015</v>
       </c>
       <c r="G48" t="n">
-        <v>-0.2650503057110056</v>
+        <v>-0.2619409429317705</v>
       </c>
       <c r="H48" t="n">
         <v>24</v>
@@ -1687,7 +1687,7 @@
         <v>45804</v>
       </c>
       <c r="B49" t="n">
-        <v>0.1719585900745464</v>
+        <v>0.1726846638866741</v>
       </c>
       <c r="C49" t="n">
         <v>24</v>
@@ -1696,13 +1696,13 @@
         <v>0</v>
       </c>
       <c r="E49" t="n">
-        <v>0.2738473161684969</v>
+        <v>0.2750083316841139</v>
       </c>
       <c r="F49" t="n">
-        <v>0.3443753578461091</v>
+        <v>0.3449165482178323</v>
       </c>
       <c r="G49" t="n">
-        <v>-0.650250194239814</v>
+        <v>-0.6554410492442078</v>
       </c>
       <c r="H49" t="n">
         <v>24</v>
@@ -1713,7 +1713,7 @@
         <v>45805</v>
       </c>
       <c r="B50" t="n">
-        <v>0.169641928249199</v>
+        <v>0.1714625668463798</v>
       </c>
       <c r="C50" t="n">
         <v>24</v>
@@ -1722,13 +1722,13 @@
         <v>0</v>
       </c>
       <c r="E50" t="n">
-        <v>0.2698224570879144</v>
+        <v>0.2727249958769598</v>
       </c>
       <c r="F50" t="n">
-        <v>0.3625868052185373</v>
+        <v>0.3631775050239592</v>
       </c>
       <c r="G50" t="n">
-        <v>0.1022279209138489</v>
+        <v>0.09930036944787901</v>
       </c>
       <c r="H50" t="n">
         <v>24</v>
@@ -1739,7 +1739,7 @@
         <v>45806</v>
       </c>
       <c r="B51" t="n">
-        <v>0.411655975958421</v>
+        <v>0.4120096329640913</v>
       </c>
       <c r="C51" t="n">
         <v>24</v>
@@ -1748,13 +1748,13 @@
         <v>0</v>
       </c>
       <c r="E51" t="n">
-        <v>0.6490403247509171</v>
+        <v>0.649620832508725</v>
       </c>
       <c r="F51" t="n">
-        <v>1.513161245800946</v>
+        <v>1.51310565675479</v>
       </c>
       <c r="G51" t="n">
-        <v>-0.8599628714346965</v>
+        <v>-0.8598262149309563</v>
       </c>
       <c r="H51" t="n">
         <v>24</v>
@@ -1765,7 +1765,7 @@
         <v>45807</v>
       </c>
       <c r="B52" t="n">
-        <v>0.1481970639998679</v>
+        <v>0.1474669579364089</v>
       </c>
       <c r="C52" t="n">
         <v>24</v>
@@ -1774,13 +1774,13 @@
         <v>0</v>
       </c>
       <c r="E52" t="n">
-        <v>0.2364901838315004</v>
+        <v>0.2353291683158763</v>
       </c>
       <c r="F52" t="n">
-        <v>0.2820514592110147</v>
+        <v>0.2822488776584991</v>
       </c>
       <c r="G52" t="n">
-        <v>-0.4533435437771582</v>
+        <v>-0.4553787556411735</v>
       </c>
       <c r="H52" t="n">
         <v>24</v>
@@ -1791,7 +1791,7 @@
         <v>45808</v>
       </c>
       <c r="B53" t="n">
-        <v>0.3641518775169039</v>
+        <v>0.3648709334104503</v>
       </c>
       <c r="C53" t="n">
         <v>24</v>
@@ -1800,13 +1800,13 @@
         <v>0</v>
       </c>
       <c r="E53" t="n">
-        <v>0.5729973161684979</v>
+        <v>0.5741583316841125</v>
       </c>
       <c r="F53" t="n">
-        <v>1.521682902006171</v>
+        <v>1.521677505171866</v>
       </c>
       <c r="G53" t="n">
-        <v>-0.9860916601845231</v>
+        <v>-0.9860775723761068</v>
       </c>
       <c r="H53" t="n">
         <v>24</v>
@@ -1817,7 +1817,7 @@
         <v>45809</v>
       </c>
       <c r="B54" t="n">
-        <v>14.70066187375627</v>
+        <v>14.69931894602372</v>
       </c>
       <c r="C54" t="n">
         <v>24</v>
@@ -1826,13 +1826,13 @@
         <v>0</v>
       </c>
       <c r="E54" t="n">
-        <v>5.355212499999999</v>
+        <v>5.355212499999997</v>
       </c>
       <c r="F54" t="n">
-        <v>24.2067284564914</v>
+        <v>24.20522383898312</v>
       </c>
       <c r="G54" t="n">
-        <v>0.8278992185115672</v>
+        <v>0.8279206123816091</v>
       </c>
       <c r="H54" t="n">
         <v>24</v>
@@ -1843,7 +1843,7 @@
         <v>45810</v>
       </c>
       <c r="B55" t="n">
-        <v>0.3844783852346306</v>
+        <v>0.3852576797566546</v>
       </c>
       <c r="C55" t="n">
         <v>24</v>
@@ -1852,13 +1852,13 @@
         <v>0</v>
       </c>
       <c r="E55" t="n">
-        <v>0.1316000000000003</v>
+        <v>0.1318791658420582</v>
       </c>
       <c r="F55" t="n">
-        <v>0.1538097964911054</v>
+        <v>0.1541634217630745</v>
       </c>
       <c r="G55" t="n">
-        <v>-0.6484688198037105</v>
+        <v>-0.6560575478198896</v>
       </c>
       <c r="H55" t="n">
         <v>24</v>
@@ -1869,7 +1869,7 @@
         <v>45811</v>
       </c>
       <c r="B56" t="n">
-        <v>0.2896854882624436</v>
+        <v>0.2864352994881342</v>
       </c>
       <c r="C56" t="n">
         <v>24</v>
@@ -1878,13 +1878,13 @@
         <v>0</v>
       </c>
       <c r="E56" t="n">
-        <v>0.09912351716483621</v>
+        <v>0.09802500082460923</v>
       </c>
       <c r="F56" t="n">
-        <v>0.1179874099809847</v>
+        <v>0.1176264782487399</v>
       </c>
       <c r="G56" t="n">
-        <v>-0.352395470945444</v>
+        <v>-0.3441339820330307</v>
       </c>
       <c r="H56" t="n">
         <v>24</v>
@@ -1895,7 +1895,7 @@
         <v>45812</v>
       </c>
       <c r="B57" t="n">
-        <v>0.9453086095982971</v>
+        <v>0.9437236535524406</v>
       </c>
       <c r="C57" t="n">
         <v>24</v>
@@ -1904,13 +1904,13 @@
         <v>0</v>
       </c>
       <c r="E57" t="n">
-        <v>0.3125096752490846</v>
+        <v>0.3119999999999997</v>
       </c>
       <c r="F57" t="n">
-        <v>0.7961382747140986</v>
+        <v>0.7962094394295794</v>
       </c>
       <c r="G57" t="n">
-        <v>-0.9671295790405716</v>
+        <v>-0.9674812678813982</v>
       </c>
       <c r="H57" t="n">
         <v>24</v>
@@ -1921,7 +1921,7 @@
         <v>45813</v>
       </c>
       <c r="B58" t="n">
-        <v>0.3032342959910067</v>
+        <v>0.3023028536796271</v>
       </c>
       <c r="C58" t="n">
         <v>24</v>
@@ -1930,13 +1930,13 @@
         <v>0</v>
       </c>
       <c r="E58" t="n">
-        <v>0.1036055085824194</v>
+        <v>0.1032958333333346</v>
       </c>
       <c r="F58" t="n">
-        <v>0.1332256161605777</v>
+        <v>0.1335270346541159</v>
       </c>
       <c r="G58" t="n">
-        <v>-1.333072770079553</v>
+        <v>-1.343641710476571</v>
       </c>
       <c r="H58" t="n">
         <v>24</v>
@@ -1947,7 +1947,7 @@
         <v>45814</v>
       </c>
       <c r="B59" t="n">
-        <v>0.162147942360988</v>
+        <v>0.162131879895953</v>
       </c>
       <c r="C59" t="n">
         <v>24</v>
@@ -1959,10 +1959,10 @@
         <v>0.05538333333333156</v>
       </c>
       <c r="F59" t="n">
-        <v>0.07294960270049645</v>
+        <v>0.07293689578693779</v>
       </c>
       <c r="G59" t="n">
-        <v>0.1141423181055312</v>
+        <v>0.1144509020100302</v>
       </c>
       <c r="H59" t="n">
         <v>24</v>
@@ -1973,7 +1973,7 @@
         <v>45815</v>
       </c>
       <c r="B60" t="n">
-        <v>0.1983864030928829</v>
+        <v>0.1966588485676918</v>
       </c>
       <c r="C60" t="n">
         <v>24</v>
@@ -1982,13 +1982,13 @@
         <v>0</v>
       </c>
       <c r="E60" t="n">
-        <v>0.06777217524908578</v>
+        <v>0.0671916674912767</v>
       </c>
       <c r="F60" t="n">
-        <v>0.08267753249311019</v>
+        <v>0.0826547332971492</v>
       </c>
       <c r="G60" t="n">
-        <v>0.01009364091681009</v>
+        <v>0.01063951974397515</v>
       </c>
       <c r="H60" t="n">
         <v>24</v>
@@ -1999,7 +1999,7 @@
         <v>45816</v>
       </c>
       <c r="B61" t="n">
-        <v>0.2332991279974546</v>
+        <v>0.2349807000194508</v>
       </c>
       <c r="C61" t="n">
         <v>24</v>
@@ -2008,13 +2008,13 @@
         <v>0</v>
       </c>
       <c r="E61" t="n">
-        <v>0.07952365808424904</v>
+        <v>0.08010416584205811</v>
       </c>
       <c r="F61" t="n">
-        <v>0.09604081525189033</v>
+        <v>0.09637330546815139</v>
       </c>
       <c r="G61" t="n">
-        <v>-1.066954391614438</v>
+        <v>-1.08129062389067</v>
       </c>
       <c r="H61" t="n">
         <v>24</v>
@@ -2025,7 +2025,7 @@
         <v>45817</v>
       </c>
       <c r="B62" t="n">
-        <v>0.1780508955611272</v>
+        <v>0.1752460173263226</v>
       </c>
       <c r="C62" t="n">
         <v>24</v>
@@ -2034,13 +2034,13 @@
         <v>0</v>
       </c>
       <c r="E62" t="n">
-        <v>0.06064435049816996</v>
+        <v>0.05969583415794263</v>
       </c>
       <c r="F62" t="n">
-        <v>0.07562321412260765</v>
+        <v>0.07591743783698734</v>
       </c>
       <c r="G62" t="n">
-        <v>-0.7877372450450426</v>
+        <v>-0.8016752382976033</v>
       </c>
       <c r="H62" t="n">
         <v>24</v>
@@ -2051,7 +2051,7 @@
         <v>45818</v>
       </c>
       <c r="B63" t="n">
-        <v>0.222700673946342</v>
+        <v>0.2182945216757885</v>
       </c>
       <c r="C63" t="n">
         <v>24</v>
@@ -2060,13 +2060,13 @@
         <v>0</v>
       </c>
       <c r="E63" t="n">
-        <v>0.07583036766300626</v>
+        <v>0.07433750082460892</v>
       </c>
       <c r="F63" t="n">
-        <v>0.09444431010450478</v>
+        <v>0.09406000319285888</v>
       </c>
       <c r="G63" t="n">
-        <v>-0.1820547129978967</v>
+        <v>-0.1724543983070506</v>
       </c>
       <c r="H63" t="n">
         <v>24</v>
@@ -2077,7 +2077,7 @@
         <v>45819</v>
       </c>
       <c r="B64" t="n">
-        <v>0.2942216498877593</v>
+        <v>0.2958373601061243</v>
       </c>
       <c r="C64" t="n">
         <v>24</v>
@@ -2086,13 +2086,13 @@
         <v>0</v>
       </c>
       <c r="E64" t="n">
-        <v>0.1001083333333336</v>
+        <v>0.1006666650174489</v>
       </c>
       <c r="F64" t="n">
-        <v>0.126723287740019</v>
+        <v>0.1273292824558042</v>
       </c>
       <c r="G64" t="n">
-        <v>-0.7337923324523068</v>
+        <v>-0.750414078564914</v>
       </c>
       <c r="H64" t="n">
         <v>24</v>
@@ -2103,7 +2103,7 @@
         <v>45820</v>
       </c>
       <c r="B65" t="n">
-        <v>1.014446050507037</v>
+        <v>1.01091563415689</v>
       </c>
       <c r="C65" t="n">
         <v>24</v>
@@ -2112,13 +2112,13 @@
         <v>0</v>
       </c>
       <c r="E65" t="n">
-        <v>0.3332485171648377</v>
+        <v>0.3320875016492195</v>
       </c>
       <c r="F65" t="n">
-        <v>0.8666748695630128</v>
+        <v>0.8665925816862676</v>
       </c>
       <c r="G65" t="n">
-        <v>-1.179970123490865</v>
+        <v>-1.179556181416112</v>
       </c>
       <c r="H65" t="n">
         <v>24</v>
@@ -2129,7 +2129,7 @@
         <v>45821</v>
       </c>
       <c r="B66" t="n">
-        <v>3.871473050185766</v>
+        <v>3.876275024153082</v>
       </c>
       <c r="C66" t="n">
         <v>24</v>
@@ -2138,13 +2138,13 @@
         <v>0</v>
       </c>
       <c r="E66" t="n">
-        <v>1.18924314950183</v>
+        <v>1.190958330859506</v>
       </c>
       <c r="F66" t="n">
-        <v>2.119137645345971</v>
+        <v>2.11916425895623</v>
       </c>
       <c r="G66" t="n">
-        <v>-0.546855252676081</v>
+        <v>-0.5468941058967924</v>
       </c>
       <c r="H66" t="n">
         <v>24</v>
@@ -2155,7 +2155,7 @@
         <v>45822</v>
       </c>
       <c r="B67" t="n">
-        <v>0.3179776630366831</v>
+        <v>0.3196557036840145</v>
       </c>
       <c r="C67" t="n">
         <v>24</v>
@@ -2164,13 +2164,13 @@
         <v>0</v>
       </c>
       <c r="E67" t="n">
-        <v>0.107977824750915</v>
+        <v>0.108558332508724</v>
       </c>
       <c r="F67" t="n">
-        <v>0.120598841824004</v>
+        <v>0.1209998812055979</v>
       </c>
       <c r="G67" t="n">
-        <v>-0.8780398658291459</v>
+        <v>-0.8905511010501999</v>
       </c>
       <c r="H67" t="n">
         <v>24</v>
@@ -2181,7 +2181,7 @@
         <v>45823</v>
       </c>
       <c r="B68" t="n">
-        <v>0.2353519116665042</v>
+        <v>0.2336150225849331</v>
       </c>
       <c r="C68" t="n">
         <v>24</v>
@@ -2190,13 +2190,13 @@
         <v>0</v>
       </c>
       <c r="E68" t="n">
-        <v>0.07988467524908582</v>
+        <v>0.07930416749127674</v>
       </c>
       <c r="F68" t="n">
-        <v>0.09919523230818555</v>
+        <v>0.09912500080295997</v>
       </c>
       <c r="G68" t="n">
-        <v>-0.3475978918116562</v>
+        <v>-0.345690333924991</v>
       </c>
       <c r="H68" t="n">
         <v>24</v>
@@ -2207,7 +2207,7 @@
         <v>45824</v>
       </c>
       <c r="B69" t="n">
-        <v>2.295078152381134</v>
+        <v>2.294564858137942</v>
       </c>
       <c r="C69" t="n">
         <v>24</v>
@@ -2216,13 +2216,13 @@
         <v>0</v>
       </c>
       <c r="E69" t="n">
-        <v>0.7452138419157507</v>
+        <v>0.7451208333333327</v>
       </c>
       <c r="F69" t="n">
-        <v>1.394168075005379</v>
+        <v>1.394179214587187</v>
       </c>
       <c r="G69" t="n">
-        <v>-1.26122002837243</v>
+        <v>-1.261256163393129</v>
       </c>
       <c r="H69" t="n">
         <v>24</v>
@@ -2233,7 +2233,7 @@
         <v>45825</v>
       </c>
       <c r="B70" t="n">
-        <v>0.8810714102698655</v>
+        <v>0.8834975731149993</v>
       </c>
       <c r="C70" t="n">
         <v>24</v>
@@ -2242,13 +2242,13 @@
         <v>0</v>
       </c>
       <c r="E70" t="n">
-        <v>0.2873319914175812</v>
+        <v>0.2881833316841146</v>
       </c>
       <c r="F70" t="n">
-        <v>0.7850622842397033</v>
+        <v>0.7850811422324497</v>
       </c>
       <c r="G70" t="n">
-        <v>-0.9630325195696041</v>
+        <v>-0.9631268287686925</v>
       </c>
       <c r="H70" t="n">
         <v>24</v>
@@ -2259,7 +2259,7 @@
         <v>45826</v>
       </c>
       <c r="B71" t="n">
-        <v>0.2319711642827757</v>
+        <v>0.2340610454837405</v>
       </c>
       <c r="C71" t="n">
         <v>24</v>
@@ -2268,13 +2268,13 @@
         <v>0</v>
       </c>
       <c r="E71" t="n">
-        <v>0.07851324141758169</v>
+        <v>0.07923124835078148</v>
       </c>
       <c r="F71" t="n">
-        <v>0.10112772351253</v>
+        <v>0.101522052842663</v>
       </c>
       <c r="G71" t="n">
-        <v>-0.6302876985068364</v>
+        <v>-0.6430265125935879</v>
       </c>
       <c r="H71" t="n">
         <v>24</v>
@@ -2285,7 +2285,7 @@
         <v>45827</v>
       </c>
       <c r="B72" t="n">
-        <v>1.600311549144033</v>
+        <v>1.596707351668318</v>
       </c>
       <c r="C72" t="n">
         <v>24</v>
@@ -2294,13 +2294,13 @@
         <v>0</v>
       </c>
       <c r="E72" t="n">
-        <v>0.5223006004981698</v>
+        <v>0.5211395849825516</v>
       </c>
       <c r="F72" t="n">
-        <v>1.132299590762515</v>
+        <v>1.132338517052953</v>
       </c>
       <c r="G72" t="n">
-        <v>-1.248287454213721</v>
+        <v>-1.248442040500756</v>
       </c>
       <c r="H72" t="n">
         <v>24</v>
@@ -2311,7 +2311,7 @@
         <v>45828</v>
       </c>
       <c r="B73" t="n">
-        <v>1.7111494206208</v>
+        <v>1.710378469844584</v>
       </c>
       <c r="C73" t="n">
         <v>24</v>
@@ -2320,13 +2320,13 @@
         <v>0</v>
       </c>
       <c r="E73" t="n">
-        <v>0.5594763419157521</v>
+        <v>0.559304165842058</v>
       </c>
       <c r="F73" t="n">
-        <v>1.189010317245771</v>
+        <v>1.189016665810993</v>
       </c>
       <c r="G73" t="n">
-        <v>-0.563590003252135</v>
+        <v>-0.5636067004657308</v>
       </c>
       <c r="H73" t="n">
         <v>24</v>
@@ -2337,7 +2337,7 @@
         <v>45829</v>
       </c>
       <c r="B74" t="n">
-        <v>0.1468022959125879</v>
+        <v>0.1485001254629494</v>
       </c>
       <c r="C74" t="n">
         <v>24</v>
@@ -2346,13 +2346,13 @@
         <v>0</v>
       </c>
       <c r="E74" t="n">
-        <v>0.04986532475091435</v>
+        <v>0.05044583250872344</v>
       </c>
       <c r="F74" t="n">
-        <v>0.06205627599589787</v>
+        <v>0.06239123099594261</v>
       </c>
       <c r="G74" t="n">
-        <v>-0.506533723398183</v>
+        <v>-0.522840949915208</v>
       </c>
       <c r="H74" t="n">
         <v>24</v>
@@ -2363,7 +2363,7 @@
         <v>45830</v>
       </c>
       <c r="B75" t="n">
-        <v>1.169065209720139</v>
+        <v>1.172357287202175</v>
       </c>
       <c r="C75" t="n">
         <v>24</v>
@@ -2372,13 +2372,13 @@
         <v>0</v>
       </c>
       <c r="E75" t="n">
-        <v>0.3853764828351635</v>
+        <v>0.3865374983507817</v>
       </c>
       <c r="F75" t="n">
-        <v>0.8917899439750132</v>
+        <v>0.89184992886271</v>
       </c>
       <c r="G75" t="n">
-        <v>-1.193995539365836</v>
+        <v>-1.194290700806224</v>
       </c>
       <c r="H75" t="n">
         <v>24</v>
@@ -2389,7 +2389,7 @@
         <v>45831</v>
       </c>
       <c r="B76" t="n">
-        <v>1.650751354472563</v>
+        <v>1.652285671282684</v>
       </c>
       <c r="C76" t="n">
         <v>24</v>
@@ -2398,13 +2398,13 @@
         <v>0</v>
       </c>
       <c r="E76" t="n">
-        <v>0.5397194914175817</v>
+        <v>0.5402999991753908</v>
       </c>
       <c r="F76" t="n">
-        <v>1.160421878376443</v>
+        <v>1.160464876226755</v>
       </c>
       <c r="G76" t="n">
-        <v>-1.191830074800264</v>
+        <v>-1.191992508358721</v>
       </c>
       <c r="H76" t="n">
         <v>24</v>
@@ -2415,7 +2415,7 @@
         <v>45832</v>
       </c>
       <c r="B77" t="n">
-        <v>1.652926879438045</v>
+        <v>1.656238773526162</v>
       </c>
       <c r="C77" t="n">
         <v>24</v>
@@ -2424,13 +2424,13 @@
         <v>0</v>
       </c>
       <c r="E77" t="n">
-        <v>0.5398889828351635</v>
+        <v>0.5410499983507817</v>
       </c>
       <c r="F77" t="n">
-        <v>1.163692400026649</v>
+        <v>1.163689308811113</v>
       </c>
       <c r="G77" t="n">
-        <v>-0.4939963685524629</v>
+        <v>-0.4939884313026335</v>
       </c>
       <c r="H77" t="n">
         <v>24</v>
@@ -2441,7 +2441,7 @@
         <v>45833</v>
       </c>
       <c r="B78" t="n">
-        <v>0.2288577240100909</v>
+        <v>0.2323824145484092</v>
       </c>
       <c r="C78" t="n">
         <v>24</v>
@@ -2450,13 +2450,13 @@
         <v>0</v>
       </c>
       <c r="E78" t="n">
-        <v>0.07789032475091535</v>
+        <v>0.07909583085950622</v>
       </c>
       <c r="F78" t="n">
-        <v>0.1041409078696721</v>
+        <v>0.1043619895631973</v>
       </c>
       <c r="G78" t="n">
-        <v>-0.6955394582826198</v>
+        <v>-0.702746052342835</v>
       </c>
       <c r="H78" t="n">
         <v>24</v>
@@ -2467,7 +2467,7 @@
         <v>45834</v>
       </c>
       <c r="B79" t="n">
-        <v>0.1949390890121194</v>
+        <v>0.1966299651788086</v>
       </c>
       <c r="C79" t="n">
         <v>24</v>
@@ -2476,13 +2476,13 @@
         <v>0</v>
       </c>
       <c r="E79" t="n">
-        <v>0.06614032475091669</v>
+        <v>0.06672083250872578</v>
       </c>
       <c r="F79" t="n">
-        <v>0.0785757679181362</v>
+        <v>0.07841901320912571</v>
       </c>
       <c r="G79" t="n">
-        <v>0.03904132886172074</v>
+        <v>0.04287163294723906</v>
       </c>
       <c r="H79" t="n">
         <v>24</v>
@@ -2493,7 +2493,7 @@
         <v>45835</v>
       </c>
       <c r="B80" t="n">
-        <v>0.9219759906752251</v>
+        <v>0.9222002878326299</v>
       </c>
       <c r="C80" t="n">
         <v>24</v>
@@ -2502,13 +2502,13 @@
         <v>0</v>
       </c>
       <c r="E80" t="n">
-        <v>0.3023430085824179</v>
+        <v>0.3024499983507812</v>
       </c>
       <c r="F80" t="n">
-        <v>0.8435615448945786</v>
+        <v>0.8436169424754546</v>
       </c>
       <c r="G80" t="n">
-        <v>-1.083677728604328</v>
+        <v>-1.083951412241087</v>
       </c>
       <c r="H80" t="n">
         <v>24</v>
@@ -2519,7 +2519,7 @@
         <v>45836</v>
       </c>
       <c r="B81" t="n">
-        <v>3.053044225527242</v>
+        <v>3.058455213802779</v>
       </c>
       <c r="C81" t="n">
         <v>24</v>
@@ -2528,13 +2528,13 @@
         <v>0</v>
       </c>
       <c r="E81" t="n">
-        <v>1.968545974252744</v>
+        <v>1.970287497526171</v>
       </c>
       <c r="F81" t="n">
-        <v>6.414663877906743</v>
+        <v>6.416656393866447</v>
       </c>
       <c r="G81" t="n">
-        <v>0.9021349334065507</v>
+        <v>0.9020741264817342</v>
       </c>
       <c r="H81" t="n">
         <v>24</v>
@@ -2545,7 +2545,7 @@
         <v>45837</v>
       </c>
       <c r="B82" t="n">
-        <v>2.882282898691216</v>
+        <v>2.882585243071706</v>
       </c>
       <c r="C82" t="n">
         <v>24</v>
@@ -2554,13 +2554,13 @@
         <v>0</v>
       </c>
       <c r="E82" t="n">
-        <v>3.626465324750914</v>
+        <v>3.627045832508724</v>
       </c>
       <c r="F82" t="n">
-        <v>9.553904173504504</v>
+        <v>9.556372088844007</v>
       </c>
       <c r="G82" t="n">
-        <v>0.9315716665290431</v>
+        <v>0.9315363098534337</v>
       </c>
       <c r="H82" t="n">
         <v>24</v>
@@ -2571,7 +2571,7 @@
         <v>45838</v>
       </c>
       <c r="B83" t="n">
-        <v>0.7822621520658904</v>
+        <v>0.7820534878860157</v>
       </c>
       <c r="C83" t="n">
         <v>23</v>
@@ -2580,13 +2580,13 @@
         <v>0</v>
       </c>
       <c r="E83" t="n">
-        <v>1.222426787086483</v>
+        <v>1.222123913473715</v>
       </c>
       <c r="F83" t="n">
-        <v>2.238605541471904</v>
+        <v>2.238401836430449</v>
       </c>
       <c r="G83" t="n">
-        <v>-1.703947487275014</v>
+        <v>-1.703455410699643</v>
       </c>
       <c r="H83" t="n">
         <v>23</v>

--- a/optimized_version/metadata/testing_daily_metrics/agus6_testing_daily_metrics.xlsx
+++ b/optimized_version/metadata/testing_daily_metrics/agus6_testing_daily_metrics.xlsx
@@ -467,7 +467,7 @@
         <v>45757</v>
       </c>
       <c r="B2" t="n">
-        <v>2.549593713028371</v>
+        <v>2.549593706799065</v>
       </c>
       <c r="C2" t="n">
         <v>1</v>
@@ -476,10 +476,10 @@
         <v>0</v>
       </c>
       <c r="E2" t="n">
-        <v>4.050050009895273</v>
+        <v>4.05004999999997</v>
       </c>
       <c r="F2" t="n">
-        <v>4.050050009895273</v>
+        <v>4.05004999999997</v>
       </c>
       <c r="G2" t="inlineStr"/>
       <c r="H2" t="n">
@@ -491,7 +491,7 @@
         <v>45758</v>
       </c>
       <c r="B3" t="n">
-        <v>0.8499060895308863</v>
+        <v>0.8499060889901227</v>
       </c>
       <c r="C3" t="n">
         <v>24</v>
@@ -500,13 +500,13 @@
         <v>0</v>
       </c>
       <c r="E3" t="n">
-        <v>1.318662500824611</v>
+        <v>1.318662500000002</v>
       </c>
       <c r="F3" t="n">
-        <v>2.960782005416208</v>
+        <v>2.960782005477327</v>
       </c>
       <c r="G3" t="n">
-        <v>-0.4782408403218494</v>
+        <v>-0.4782408403828795</v>
       </c>
       <c r="H3" t="n">
         <v>24</v>
@@ -517,7 +517,7 @@
         <v>45759</v>
       </c>
       <c r="B4" t="n">
-        <v>0.8678273405686965</v>
+        <v>0.8678273394943194</v>
       </c>
       <c r="C4" t="n">
         <v>24</v>
@@ -526,13 +526,13 @@
         <v>0</v>
       </c>
       <c r="E4" t="n">
-        <v>1.361320834982547</v>
+        <v>1.36132083333333</v>
       </c>
       <c r="F4" t="n">
-        <v>2.459727272199246</v>
+        <v>2.45972727108617</v>
       </c>
       <c r="G4" t="n">
-        <v>0.438110504728929</v>
+        <v>0.438110505237462</v>
       </c>
       <c r="H4" t="n">
         <v>24</v>
@@ -543,7 +543,7 @@
         <v>45760</v>
       </c>
       <c r="B5" t="n">
-        <v>6.228736109019021</v>
+        <v>6.228736110627551</v>
       </c>
       <c r="C5" t="n">
         <v>24</v>
@@ -552,13 +552,13 @@
         <v>0</v>
       </c>
       <c r="E5" t="n">
-        <v>8.380220830859507</v>
+        <v>8.380220833333333</v>
       </c>
       <c r="F5" t="n">
-        <v>14.75736364273668</v>
+        <v>14.75736364385167</v>
       </c>
       <c r="G5" t="n">
-        <v>0.7972860951061722</v>
+        <v>0.7972860950755405</v>
       </c>
       <c r="H5" t="n">
         <v>24</v>
@@ -569,7 +569,7 @@
         <v>45761</v>
       </c>
       <c r="B6" t="n">
-        <v>2.325395562539609</v>
+        <v>2.32539556205882</v>
       </c>
       <c r="C6" t="n">
         <v>24</v>
@@ -578,13 +578,13 @@
         <v>0</v>
       </c>
       <c r="E6" t="n">
-        <v>4.049820834157941</v>
+        <v>4.049820833333333</v>
       </c>
       <c r="F6" t="n">
-        <v>5.956669549609707</v>
+        <v>5.956669548567668</v>
       </c>
       <c r="G6" t="n">
-        <v>0.421974013132407</v>
+        <v>0.4219740133346426</v>
       </c>
       <c r="H6" t="n">
         <v>24</v>
@@ -595,7 +595,7 @@
         <v>45762</v>
       </c>
       <c r="B7" t="n">
-        <v>0.7393897584218099</v>
+        <v>0.7393897574964726</v>
       </c>
       <c r="C7" t="n">
         <v>24</v>
@@ -604,13 +604,13 @@
         <v>0</v>
       </c>
       <c r="E7" t="n">
-        <v>1.314325001649211</v>
+        <v>1.314324999999994</v>
       </c>
       <c r="F7" t="n">
-        <v>2.118143456201913</v>
+        <v>2.118143456543958</v>
       </c>
       <c r="G7" t="n">
-        <v>0.6247943505410205</v>
+        <v>0.6247943504198415</v>
       </c>
       <c r="H7" t="n">
         <v>24</v>
@@ -621,7 +621,7 @@
         <v>45763</v>
       </c>
       <c r="B8" t="n">
-        <v>2.456302627248769</v>
+        <v>2.456302628636398</v>
       </c>
       <c r="C8" t="n">
         <v>24</v>
@@ -630,13 +630,13 @@
         <v>0</v>
       </c>
       <c r="E8" t="n">
-        <v>4.309587497526177</v>
+        <v>4.309587500000003</v>
       </c>
       <c r="F8" t="n">
-        <v>6.841717512595611</v>
+        <v>6.841717512605428</v>
       </c>
       <c r="G8" t="n">
-        <v>0.0641708241149096</v>
+        <v>0.06417082411222419</v>
       </c>
       <c r="H8" t="n">
         <v>24</v>
@@ -647,7 +647,7 @@
         <v>45764</v>
       </c>
       <c r="B9" t="n">
-        <v>11.7897559045285</v>
+        <v>11.78975590374235</v>
       </c>
       <c r="C9" t="n">
         <v>24</v>
@@ -656,13 +656,13 @@
         <v>0</v>
       </c>
       <c r="E9" t="n">
-        <v>14.03792916749128</v>
+        <v>14.03792916666667</v>
       </c>
       <c r="F9" t="n">
-        <v>21.46410990193405</v>
+        <v>21.46410990057977</v>
       </c>
       <c r="G9" t="n">
-        <v>0.4626008460991505</v>
+        <v>0.4626008461669647</v>
       </c>
       <c r="H9" t="n">
         <v>24</v>
@@ -673,7 +673,7 @@
         <v>45765</v>
       </c>
       <c r="B10" t="n">
-        <v>4.543894053567266</v>
+        <v>4.543894056742895</v>
       </c>
       <c r="C10" t="n">
         <v>24</v>
@@ -682,13 +682,13 @@
         <v>0</v>
       </c>
       <c r="E10" t="n">
-        <v>4.652295830034894</v>
+        <v>4.652295833333327</v>
       </c>
       <c r="F10" t="n">
-        <v>7.396939364366955</v>
+        <v>7.396939364288333</v>
       </c>
       <c r="G10" t="n">
-        <v>0.5321025065591561</v>
+        <v>0.5321025065691027</v>
       </c>
       <c r="H10" t="n">
         <v>24</v>
@@ -699,7 +699,7 @@
         <v>45766</v>
       </c>
       <c r="B11" t="n">
-        <v>5.005756000996196</v>
+        <v>5.005756000807752</v>
       </c>
       <c r="C11" t="n">
         <v>24</v>
@@ -711,10 +711,10 @@
         <v>5.452875</v>
       </c>
       <c r="F11" t="n">
-        <v>8.425751444509929</v>
+        <v>8.425751444480589</v>
       </c>
       <c r="G11" t="n">
-        <v>0.1164594533584603</v>
+        <v>0.1164594533646137</v>
       </c>
       <c r="H11" t="n">
         <v>24</v>
@@ -725,7 +725,7 @@
         <v>45767</v>
       </c>
       <c r="B12" t="n">
-        <v>1.741731300093242</v>
+        <v>1.741731304221119</v>
       </c>
       <c r="C12" t="n">
         <v>24</v>
@@ -734,13 +734,13 @@
         <v>0</v>
       </c>
       <c r="E12" t="n">
-        <v>2.471754161719014</v>
+        <v>2.471754166666665</v>
       </c>
       <c r="F12" t="n">
-        <v>7.024863807626811</v>
+        <v>7.024863810779536</v>
       </c>
       <c r="G12" t="n">
-        <v>0.9209705194464067</v>
+        <v>0.9209705193754707</v>
       </c>
       <c r="H12" t="n">
         <v>24</v>
@@ -751,7 +751,7 @@
         <v>45768</v>
       </c>
       <c r="B13" t="n">
-        <v>0.2552101402589769</v>
+        <v>0.2552101407669061</v>
       </c>
       <c r="C13" t="n">
         <v>24</v>
@@ -760,13 +760,13 @@
         <v>0</v>
       </c>
       <c r="E13" t="n">
-        <v>0.4078416658420565</v>
+        <v>0.407841666666665</v>
       </c>
       <c r="F13" t="n">
-        <v>0.4771787482453187</v>
+        <v>0.4771787488282902</v>
       </c>
       <c r="G13" t="n">
-        <v>-0.3104377771095741</v>
+        <v>-0.3104377803115101</v>
       </c>
       <c r="H13" t="n">
         <v>24</v>
@@ -777,7 +777,7 @@
         <v>45769</v>
       </c>
       <c r="B14" t="n">
-        <v>0.7741169417354196</v>
+        <v>0.7741169422255975</v>
       </c>
       <c r="C14" t="n">
         <v>24</v>
@@ -786,13 +786,13 @@
         <v>0</v>
       </c>
       <c r="E14" t="n">
-        <v>1.219074999175387</v>
+        <v>1.219074999999995</v>
       </c>
       <c r="F14" t="n">
-        <v>2.288378225647079</v>
+        <v>2.288378225676428</v>
       </c>
       <c r="G14" t="n">
-        <v>-0.8820752517660728</v>
+        <v>-0.8820752518143506</v>
       </c>
       <c r="H14" t="n">
         <v>24</v>
@@ -803,7 +803,7 @@
         <v>45770</v>
       </c>
       <c r="B15" t="n">
-        <v>0.2574270715459003</v>
+        <v>0.2574270710251551</v>
       </c>
       <c r="C15" t="n">
         <v>24</v>
@@ -812,13 +812,13 @@
         <v>0</v>
       </c>
       <c r="E15" t="n">
-        <v>0.411350000824618</v>
+        <v>0.4113500000000094</v>
       </c>
       <c r="F15" t="n">
-        <v>0.5051511848203936</v>
+        <v>0.5051511852901164</v>
       </c>
       <c r="G15" t="n">
-        <v>-0.4526917315278509</v>
+        <v>-0.4526917342294678</v>
       </c>
       <c r="H15" t="n">
         <v>24</v>
@@ -829,7 +829,7 @@
         <v>45771</v>
       </c>
       <c r="B16" t="n">
-        <v>1.196374832436242</v>
+        <v>1.196374831843493</v>
       </c>
       <c r="C16" t="n">
         <v>24</v>
@@ -838,13 +838,13 @@
         <v>0</v>
       </c>
       <c r="E16" t="n">
-        <v>1.792575000824609</v>
+        <v>1.792575</v>
       </c>
       <c r="F16" t="n">
-        <v>5.138669825092268</v>
+        <v>5.138669825126599</v>
       </c>
       <c r="G16" t="n">
-        <v>0.4419177743347179</v>
+        <v>0.4419177743272606</v>
       </c>
       <c r="H16" t="n">
         <v>24</v>
@@ -855,7 +855,7 @@
         <v>45772</v>
       </c>
       <c r="B17" t="n">
-        <v>0.2592593750661586</v>
+        <v>0.2592593755737681</v>
       </c>
       <c r="C17" t="n">
         <v>24</v>
@@ -864,13 +864,13 @@
         <v>0</v>
       </c>
       <c r="E17" t="n">
-        <v>0.414795832508716</v>
+        <v>0.4147958333333245</v>
       </c>
       <c r="F17" t="n">
-        <v>0.5078532141224184</v>
+        <v>0.5078532137012267</v>
       </c>
       <c r="G17" t="n">
-        <v>-0.3963970198086237</v>
+        <v>-0.3963970174924003</v>
       </c>
       <c r="H17" t="n">
         <v>24</v>
@@ -881,7 +881,7 @@
         <v>45773</v>
       </c>
       <c r="B18" t="n">
-        <v>0.6977935288212251</v>
+        <v>0.6977935293365999</v>
       </c>
       <c r="C18" t="n">
         <v>24</v>
@@ -890,13 +890,13 @@
         <v>0</v>
       </c>
       <c r="E18" t="n">
-        <v>1.062587499175397</v>
+        <v>1.062587500000005</v>
       </c>
       <c r="F18" t="n">
-        <v>2.33103256709305</v>
+        <v>2.331032566982573</v>
       </c>
       <c r="G18" t="n">
-        <v>0.7523615496960434</v>
+        <v>0.7523615497195166</v>
       </c>
       <c r="H18" t="n">
         <v>24</v>
@@ -907,7 +907,7 @@
         <v>45774</v>
       </c>
       <c r="B19" t="n">
-        <v>4.268978695760897</v>
+        <v>4.268978695075024</v>
       </c>
       <c r="C19" t="n">
         <v>24</v>
@@ -916,13 +916,13 @@
         <v>0</v>
       </c>
       <c r="E19" t="n">
-        <v>5.47392083415794</v>
+        <v>5.473920833333331</v>
       </c>
       <c r="F19" t="n">
-        <v>11.23101033024361</v>
+        <v>11.23101032940343</v>
       </c>
       <c r="G19" t="n">
-        <v>0.5623944205649635</v>
+        <v>0.5623944206304371</v>
       </c>
       <c r="H19" t="n">
         <v>24</v>
@@ -933,7 +933,7 @@
         <v>45775</v>
       </c>
       <c r="B20" t="n">
-        <v>0.9937890303145369</v>
+        <v>0.9937890308303964</v>
       </c>
       <c r="C20" t="n">
         <v>24</v>
@@ -942,13 +942,13 @@
         <v>0</v>
       </c>
       <c r="E20" t="n">
-        <v>1.512966665842061</v>
+        <v>1.51296666666667</v>
       </c>
       <c r="F20" t="n">
-        <v>3.519929172393698</v>
+        <v>3.519929175187104</v>
       </c>
       <c r="G20" t="n">
-        <v>0.8160754269239024</v>
+        <v>0.8160754266319784</v>
       </c>
       <c r="H20" t="n">
         <v>24</v>
@@ -959,7 +959,7 @@
         <v>45776</v>
       </c>
       <c r="B21" t="n">
-        <v>0.1693222584874468</v>
+        <v>0.1693222584827396</v>
       </c>
       <c r="C21" t="n">
         <v>24</v>
@@ -971,10 +971,10 @@
         <v>0.2699916666666695</v>
       </c>
       <c r="F21" t="n">
-        <v>0.3296899073742</v>
+        <v>0.3296899073371826</v>
       </c>
       <c r="G21" t="n">
-        <v>-0.7586815534795022</v>
+        <v>-0.758681553084575</v>
       </c>
       <c r="H21" t="n">
         <v>24</v>
@@ -985,7 +985,7 @@
         <v>45777</v>
       </c>
       <c r="B22" t="n">
-        <v>0.2391032300795721</v>
+        <v>0.2391032300726561</v>
       </c>
       <c r="C22" t="n">
         <v>24</v>
@@ -997,10 +997,10 @@
         <v>0.3796416666666609</v>
       </c>
       <c r="F22" t="n">
-        <v>0.6515774166115732</v>
+        <v>0.6515774167357243</v>
       </c>
       <c r="G22" t="n">
-        <v>-0.9757911425549577</v>
+        <v>-0.9757911433078899</v>
       </c>
       <c r="H22" t="n">
         <v>24</v>
@@ -1011,7 +1011,7 @@
         <v>45778</v>
       </c>
       <c r="B23" t="n">
-        <v>1.584378996469918</v>
+        <v>1.584378998141013</v>
       </c>
       <c r="C23" t="n">
         <v>24</v>
@@ -1020,13 +1020,13 @@
         <v>0</v>
       </c>
       <c r="E23" t="n">
-        <v>2.340479164192843</v>
+        <v>2.340479166666668</v>
       </c>
       <c r="F23" t="n">
-        <v>6.067672342321204</v>
+        <v>6.067672342353916</v>
       </c>
       <c r="G23" t="n">
-        <v>0.6880334642483719</v>
+        <v>0.6880334642450081</v>
       </c>
       <c r="H23" t="n">
         <v>24</v>
@@ -1037,7 +1037,7 @@
         <v>45779</v>
       </c>
       <c r="B24" t="n">
-        <v>0.3058898578795372</v>
+        <v>0.3058898573514979</v>
       </c>
       <c r="C24" t="n">
         <v>24</v>
@@ -1046,13 +1046,13 @@
         <v>0</v>
       </c>
       <c r="E24" t="n">
-        <v>0.484750000824602</v>
+        <v>0.4847499999999935</v>
       </c>
       <c r="F24" t="n">
-        <v>0.7780258473397055</v>
+        <v>0.7780258468285817</v>
       </c>
       <c r="G24" t="n">
-        <v>-1.255459044102378</v>
+        <v>-1.255459041138932</v>
       </c>
       <c r="H24" t="n">
         <v>24</v>
@@ -1063,7 +1063,7 @@
         <v>45780</v>
       </c>
       <c r="B25" t="n">
-        <v>0.1031682285552962</v>
+        <v>0.1031682295911855</v>
       </c>
       <c r="C25" t="n">
         <v>24</v>
@@ -1072,13 +1072,13 @@
         <v>0</v>
       </c>
       <c r="E25" t="n">
-        <v>0.1636499983507823</v>
+        <v>0.1636499999999993</v>
       </c>
       <c r="F25" t="n">
-        <v>0.2322904006582356</v>
+        <v>0.2322904019397506</v>
       </c>
       <c r="G25" t="n">
-        <v>-0.09829021030531737</v>
+        <v>-0.09829022242355689</v>
       </c>
       <c r="H25" t="n">
         <v>24</v>
@@ -1089,7 +1089,7 @@
         <v>45781</v>
       </c>
       <c r="B26" t="n">
-        <v>0.2379749977461462</v>
+        <v>0.2379749972185666</v>
       </c>
       <c r="C26" t="n">
         <v>24</v>
@@ -1098,13 +1098,13 @@
         <v>0</v>
       </c>
       <c r="E26" t="n">
-        <v>0.3772083341579512</v>
+        <v>0.3772083333333427</v>
       </c>
       <c r="F26" t="n">
-        <v>0.5016425616976303</v>
+        <v>0.501642560328906</v>
       </c>
       <c r="G26" t="n">
-        <v>-0.5011440121889335</v>
+        <v>-0.5011440039972355</v>
       </c>
       <c r="H26" t="n">
         <v>24</v>
@@ -1115,7 +1115,7 @@
         <v>45782</v>
       </c>
       <c r="B27" t="n">
-        <v>0.2263283616096268</v>
+        <v>0.2263283621260576</v>
       </c>
       <c r="C27" t="n">
         <v>24</v>
@@ -1124,13 +1124,13 @@
         <v>0</v>
       </c>
       <c r="E27" t="n">
-        <v>0.3589916658420632</v>
+        <v>0.3589916666666717</v>
       </c>
       <c r="F27" t="n">
-        <v>0.5419092168206023</v>
+        <v>0.5419092180660914</v>
       </c>
       <c r="G27" t="n">
-        <v>-2.680206218131883</v>
+        <v>-2.680206235048579</v>
       </c>
       <c r="H27" t="n">
         <v>24</v>
@@ -1141,7 +1141,7 @@
         <v>45783</v>
       </c>
       <c r="B28" t="n">
-        <v>0.4567828384538801</v>
+        <v>0.4567828389583402</v>
       </c>
       <c r="C28" t="n">
         <v>24</v>
@@ -1150,13 +1150,13 @@
         <v>0</v>
       </c>
       <c r="E28" t="n">
-        <v>0.7184791658420527</v>
+        <v>0.7184791666666612</v>
       </c>
       <c r="F28" t="n">
-        <v>1.680365049264694</v>
+        <v>1.680365049376679</v>
       </c>
       <c r="G28" t="n">
-        <v>-1.003049273974213</v>
+        <v>-1.003049274241192</v>
       </c>
       <c r="H28" t="n">
         <v>24</v>
@@ -1167,7 +1167,7 @@
         <v>45784</v>
       </c>
       <c r="B29" t="n">
-        <v>0.5051346814479134</v>
+        <v>0.5051346809112124</v>
       </c>
       <c r="C29" t="n">
         <v>24</v>
@@ -1176,13 +1176,13 @@
         <v>0</v>
       </c>
       <c r="E29" t="n">
-        <v>0.7941625008246085</v>
+        <v>0.7941625</v>
       </c>
       <c r="F29" t="n">
-        <v>1.633939136739462</v>
+        <v>1.633939136973379</v>
       </c>
       <c r="G29" t="n">
-        <v>-1.04730455518096</v>
+        <v>-1.04730455576715</v>
       </c>
       <c r="H29" t="n">
         <v>24</v>
@@ -1193,7 +1193,7 @@
         <v>45785</v>
       </c>
       <c r="B30" t="n">
-        <v>0.2177308444845783</v>
+        <v>0.2177308439617515</v>
       </c>
       <c r="C30" t="n">
         <v>24</v>
@@ -1202,13 +1202,13 @@
         <v>0</v>
       </c>
       <c r="E30" t="n">
-        <v>0.3458500008246048</v>
+        <v>0.3458499999999963</v>
       </c>
       <c r="F30" t="n">
-        <v>0.4078312293168171</v>
+        <v>0.407831228369439</v>
       </c>
       <c r="G30" t="n">
-        <v>-0.34241209417501</v>
+        <v>-0.3424120879382546</v>
       </c>
       <c r="H30" t="n">
         <v>24</v>
@@ -1219,7 +1219,7 @@
         <v>45786</v>
       </c>
       <c r="B31" t="n">
-        <v>0.1509142014691166</v>
+        <v>0.1509142019836189</v>
       </c>
       <c r="C31" t="n">
         <v>24</v>
@@ -1228,13 +1228,13 @@
         <v>0</v>
       </c>
       <c r="E31" t="n">
-        <v>0.2402458325087219</v>
+        <v>0.2402458333333305</v>
       </c>
       <c r="F31" t="n">
-        <v>0.3207429345344142</v>
+        <v>0.3207429357496939</v>
       </c>
       <c r="G31" t="n">
-        <v>0.5822778339853716</v>
+        <v>0.5822778308199128</v>
       </c>
       <c r="H31" t="n">
         <v>24</v>
@@ -1245,7 +1245,7 @@
         <v>45787</v>
       </c>
       <c r="B32" t="n">
-        <v>0.1354434588238334</v>
+        <v>0.135443458299387</v>
       </c>
       <c r="C32" t="n">
         <v>24</v>
@@ -1254,13 +1254,13 @@
         <v>0</v>
       </c>
       <c r="E32" t="n">
-        <v>0.2151000008246129</v>
+        <v>0.2151000000000044</v>
       </c>
       <c r="F32" t="n">
-        <v>0.2789753104403208</v>
+        <v>0.2789753095407083</v>
       </c>
       <c r="G32" t="n">
-        <v>0.4885756359100439</v>
+        <v>0.4885756392084268</v>
       </c>
       <c r="H32" t="n">
         <v>24</v>
@@ -1271,7 +1271,7 @@
         <v>45788</v>
       </c>
       <c r="B33" t="n">
-        <v>0.2581700491521485</v>
+        <v>0.2581700481054369</v>
       </c>
       <c r="C33" t="n">
         <v>24</v>
@@ -1280,13 +1280,13 @@
         <v>0</v>
       </c>
       <c r="E33" t="n">
-        <v>0.4088125016492133</v>
+        <v>0.4088124999999962</v>
       </c>
       <c r="F33" t="n">
-        <v>0.5344068238251573</v>
+        <v>0.5344068238087238</v>
       </c>
       <c r="G33" t="n">
-        <v>-0.4115527781113353</v>
+        <v>-0.4115527780245227</v>
       </c>
       <c r="H33" t="n">
         <v>24</v>
@@ -1297,7 +1297,7 @@
         <v>45789</v>
       </c>
       <c r="B34" t="n">
-        <v>5.650626198054603</v>
+        <v>5.650626197450896</v>
       </c>
       <c r="C34" t="n">
         <v>24</v>
@@ -1306,13 +1306,13 @@
         <v>0</v>
       </c>
       <c r="E34" t="n">
-        <v>6.557570834157938</v>
+        <v>6.55757083333333</v>
       </c>
       <c r="F34" t="n">
-        <v>18.04408471282172</v>
+        <v>18.04408471284057</v>
       </c>
       <c r="G34" t="n">
-        <v>0.5744191505150515</v>
+        <v>0.5744191505141625</v>
       </c>
       <c r="H34" t="n">
         <v>24</v>
@@ -1323,7 +1323,7 @@
         <v>45790</v>
       </c>
       <c r="B35" t="n">
-        <v>0.3039538143032038</v>
+        <v>0.30395381273789</v>
       </c>
       <c r="C35" t="n">
         <v>24</v>
@@ -1332,13 +1332,13 @@
         <v>0</v>
       </c>
       <c r="E35" t="n">
-        <v>0.4820916691404887</v>
+        <v>0.4820916666666631</v>
       </c>
       <c r="F35" t="n">
-        <v>0.7842735454737453</v>
+        <v>0.7842735454971395</v>
       </c>
       <c r="G35" t="n">
-        <v>-1.054524834631529</v>
+        <v>-1.054524834754099</v>
       </c>
       <c r="H35" t="n">
         <v>24</v>
@@ -1349,7 +1349,7 @@
         <v>45791</v>
       </c>
       <c r="B36" t="n">
-        <v>0.1526977729451902</v>
+        <v>0.1526977734587781</v>
       </c>
       <c r="C36" t="n">
         <v>24</v>
@@ -1358,13 +1358,13 @@
         <v>0</v>
       </c>
       <c r="E36" t="n">
-        <v>0.2425278325087206</v>
+        <v>0.2425278333333291</v>
       </c>
       <c r="F36" t="n">
-        <v>0.3298493156191968</v>
+        <v>0.3298493155609077</v>
       </c>
       <c r="G36" t="n">
-        <v>0.04002774407137344</v>
+        <v>0.04002774441065515</v>
       </c>
       <c r="H36" t="n">
         <v>24</v>
@@ -1375,7 +1375,7 @@
         <v>45792</v>
       </c>
       <c r="B37" t="n">
-        <v>0.001334044205862042</v>
+        <v>0.001334050438549693</v>
       </c>
       <c r="C37" t="n">
         <v>24</v>
@@ -1384,13 +1384,13 @@
         <v>0</v>
       </c>
       <c r="E37" t="n">
-        <v>0.002117990104692306</v>
+        <v>0.002117999999994661</v>
       </c>
       <c r="F37" t="n">
-        <v>0.002117990104692306</v>
+        <v>0.002117999999994661</v>
       </c>
       <c r="G37" t="n">
-        <v>0.9954419251518141</v>
+        <v>0.9954418825608369</v>
       </c>
       <c r="H37" t="n">
         <v>24</v>
@@ -1401,7 +1401,7 @@
         <v>45793</v>
       </c>
       <c r="B38" t="n">
-        <v>3.309217197753584</v>
+        <v>3.309217195942805</v>
       </c>
       <c r="C38" t="n">
         <v>24</v>
@@ -1410,13 +1410,13 @@
         <v>0</v>
       </c>
       <c r="E38" t="n">
-        <v>4.349204169140489</v>
+        <v>4.349204166666664</v>
       </c>
       <c r="F38" t="n">
-        <v>10.4678923416699</v>
+        <v>10.46789234166394</v>
       </c>
       <c r="G38" t="n">
-        <v>0.7961633922231199</v>
+        <v>0.7961633922233519</v>
       </c>
       <c r="H38" t="n">
         <v>24</v>
@@ -1427,7 +1427,7 @@
         <v>45794</v>
       </c>
       <c r="B39" t="n">
-        <v>1.288493345868907</v>
+        <v>1.288493344392178</v>
       </c>
       <c r="C39" t="n">
         <v>24</v>
@@ -1436,13 +1436,13 @@
         <v>0</v>
       </c>
       <c r="E39" t="n">
-        <v>1.62052083498255</v>
+        <v>1.620520833333333</v>
       </c>
       <c r="F39" t="n">
-        <v>6.876455572279967</v>
+        <v>6.876455570277468</v>
       </c>
       <c r="G39" t="n">
-        <v>0.8154231753440355</v>
+        <v>0.8154231754515371</v>
       </c>
       <c r="H39" t="n">
         <v>24</v>
@@ -1453,7 +1453,7 @@
         <v>45795</v>
       </c>
       <c r="B40" t="n">
-        <v>0.1718729429307247</v>
+        <v>0.1718729435870379</v>
       </c>
       <c r="C40" t="n">
         <v>24</v>
@@ -1462,13 +1462,13 @@
         <v>0</v>
       </c>
       <c r="E40" t="n">
-        <v>0.2148958325087271</v>
+        <v>0.2148958333333356</v>
       </c>
       <c r="F40" t="n">
-        <v>0.2676524414399322</v>
+        <v>0.2676524425444322</v>
       </c>
       <c r="G40" t="n">
-        <v>-0.005266884594868904</v>
+        <v>-0.005266892891578223</v>
       </c>
       <c r="H40" t="n">
         <v>24</v>
@@ -1479,7 +1479,7 @@
         <v>45796</v>
       </c>
       <c r="B41" t="n">
-        <v>1.145753084713907</v>
+        <v>1.145753084609163</v>
       </c>
       <c r="C41" t="n">
         <v>24</v>
@@ -1491,10 +1491,10 @@
         <v>1.6781</v>
       </c>
       <c r="F41" t="n">
-        <v>5.150699360314504</v>
+        <v>5.150699363031517</v>
       </c>
       <c r="G41" t="n">
-        <v>0.7924828502507149</v>
+        <v>0.7924828500317828</v>
       </c>
       <c r="H41" t="n">
         <v>24</v>
@@ -1505,7 +1505,7 @@
         <v>45797</v>
       </c>
       <c r="B42" t="n">
-        <v>0.4450071692015216</v>
+        <v>0.4450071697063379</v>
       </c>
       <c r="C42" t="n">
         <v>24</v>
@@ -1514,13 +1514,13 @@
         <v>0</v>
       </c>
       <c r="E42" t="n">
-        <v>0.7019999991753991</v>
+        <v>0.7020000000000076</v>
       </c>
       <c r="F42" t="n">
-        <v>1.202586813473488</v>
+        <v>1.2025868135676</v>
       </c>
       <c r="G42" t="n">
-        <v>-0.6680795469309631</v>
+        <v>-0.6680795471920433</v>
       </c>
       <c r="H42" t="n">
         <v>24</v>
@@ -1531,7 +1531,7 @@
         <v>45798</v>
       </c>
       <c r="B43" t="n">
-        <v>0.2365633259707147</v>
+        <v>0.2365633254456861</v>
       </c>
       <c r="C43" t="n">
         <v>24</v>
@@ -1540,13 +1540,13 @@
         <v>0</v>
       </c>
       <c r="E43" t="n">
-        <v>0.3762666674912782</v>
+        <v>0.3762666666666696</v>
       </c>
       <c r="F43" t="n">
-        <v>0.4673877569233583</v>
+        <v>0.4673877565790566</v>
       </c>
       <c r="G43" t="n">
-        <v>-0.9456281870347871</v>
+        <v>-0.9456281841682888</v>
       </c>
       <c r="H43" t="n">
         <v>24</v>
@@ -1557,7 +1557,7 @@
         <v>45799</v>
       </c>
       <c r="B44" t="n">
-        <v>0.1764963820379925</v>
+        <v>0.1764963825509624</v>
       </c>
       <c r="C44" t="n">
         <v>24</v>
@@ -1566,13 +1566,13 @@
         <v>0</v>
       </c>
       <c r="E44" t="n">
-        <v>0.2805374991753951</v>
+        <v>0.2805375000000036</v>
       </c>
       <c r="F44" t="n">
-        <v>0.3498354363273879</v>
+        <v>0.349835437503597</v>
       </c>
       <c r="G44" t="n">
-        <v>-0.1901075369426661</v>
+        <v>-0.1901075449453733</v>
       </c>
       <c r="H44" t="n">
         <v>24</v>
@@ -1583,7 +1583,7 @@
         <v>45800</v>
       </c>
       <c r="B45" t="n">
-        <v>0.8629512491131369</v>
+        <v>0.8629512501191877</v>
       </c>
       <c r="C45" t="n">
         <v>24</v>
@@ -1592,13 +1592,13 @@
         <v>0</v>
       </c>
       <c r="E45" t="n">
-        <v>1.359887498350792</v>
+        <v>1.359887500000009</v>
       </c>
       <c r="F45" t="n">
-        <v>2.415575037240385</v>
+        <v>2.415575037301337</v>
       </c>
       <c r="G45" t="n">
-        <v>-1.263903505439897</v>
+        <v>-1.263903505554146</v>
       </c>
       <c r="H45" t="n">
         <v>24</v>
@@ -1609,7 +1609,7 @@
         <v>45801</v>
       </c>
       <c r="B46" t="n">
-        <v>0.2124823176918161</v>
+        <v>0.2124823192400131</v>
       </c>
       <c r="C46" t="n">
         <v>24</v>
@@ -1618,13 +1618,13 @@
         <v>0</v>
       </c>
       <c r="E46" t="n">
-        <v>0.3385124975261687</v>
+        <v>0.3385124999999943</v>
       </c>
       <c r="F46" t="n">
-        <v>0.4368084671911842</v>
+        <v>0.4368084665598082</v>
       </c>
       <c r="G46" t="n">
-        <v>-0.1262680008943979</v>
+        <v>-0.126267997638515</v>
       </c>
       <c r="H46" t="n">
         <v>24</v>
@@ -1635,7 +1635,7 @@
         <v>45802</v>
       </c>
       <c r="B47" t="n">
-        <v>5.702635964250892</v>
+        <v>5.70263596598233</v>
       </c>
       <c r="C47" t="n">
         <v>24</v>
@@ -1644,13 +1644,13 @@
         <v>0</v>
       </c>
       <c r="E47" t="n">
-        <v>6.601333330859501</v>
+        <v>6.601333333333327</v>
       </c>
       <c r="F47" t="n">
-        <v>13.19519753829305</v>
+        <v>13.19519753830916</v>
       </c>
       <c r="G47" t="n">
-        <v>0.8142103662957914</v>
+        <v>0.8142103662953377</v>
       </c>
       <c r="H47" t="n">
         <v>24</v>
@@ -1661,7 +1661,7 @@
         <v>45803</v>
       </c>
       <c r="B48" t="n">
-        <v>0.1589435093828475</v>
+        <v>0.1589435083419043</v>
       </c>
       <c r="C48" t="n">
         <v>24</v>
@@ -1670,13 +1670,13 @@
         <v>0</v>
       </c>
       <c r="E48" t="n">
-        <v>0.2529583349825562</v>
+        <v>0.2529583333333392</v>
       </c>
       <c r="F48" t="n">
-        <v>0.31448910995015</v>
+        <v>0.314489109509382</v>
       </c>
       <c r="G48" t="n">
-        <v>-0.2619409429317705</v>
+        <v>-0.2619409393944576</v>
       </c>
       <c r="H48" t="n">
         <v>24</v>
@@ -1687,7 +1687,7 @@
         <v>45804</v>
       </c>
       <c r="B49" t="n">
-        <v>0.1726846638866741</v>
+        <v>0.1726846649180586</v>
       </c>
       <c r="C49" t="n">
         <v>24</v>
@@ -1696,13 +1696,13 @@
         <v>0</v>
       </c>
       <c r="E49" t="n">
-        <v>0.2750083316841139</v>
+        <v>0.275008333333331</v>
       </c>
       <c r="F49" t="n">
-        <v>0.3449165482178323</v>
+        <v>0.3449165490859128</v>
       </c>
       <c r="G49" t="n">
-        <v>-0.6554410492442078</v>
+        <v>-0.6554410575769831</v>
       </c>
       <c r="H49" t="n">
         <v>24</v>
@@ -1713,7 +1713,7 @@
         <v>45805</v>
       </c>
       <c r="B50" t="n">
-        <v>0.1714625668463798</v>
+        <v>0.1714625694325883</v>
       </c>
       <c r="C50" t="n">
         <v>24</v>
@@ -1722,13 +1722,13 @@
         <v>0</v>
       </c>
       <c r="E50" t="n">
-        <v>0.2727249958769598</v>
+        <v>0.2727250000000024</v>
       </c>
       <c r="F50" t="n">
-        <v>0.3631775050239592</v>
+        <v>0.3631775059572639</v>
       </c>
       <c r="G50" t="n">
-        <v>0.09930036944787901</v>
+        <v>0.09930036481858784</v>
       </c>
       <c r="H50" t="n">
         <v>24</v>
@@ -1739,7 +1739,7 @@
         <v>45806</v>
       </c>
       <c r="B51" t="n">
-        <v>0.4120096329640913</v>
+        <v>0.4120096334664594</v>
       </c>
       <c r="C51" t="n">
         <v>24</v>
@@ -1748,13 +1748,13 @@
         <v>0</v>
       </c>
       <c r="E51" t="n">
-        <v>0.649620832508725</v>
+        <v>0.6496208333333335</v>
       </c>
       <c r="F51" t="n">
-        <v>1.51310565675479</v>
+        <v>1.513105656698603</v>
       </c>
       <c r="G51" t="n">
-        <v>-0.8598262149309563</v>
+        <v>-0.8598262147928319</v>
       </c>
       <c r="H51" t="n">
         <v>24</v>
@@ -1765,7 +1765,7 @@
         <v>45807</v>
       </c>
       <c r="B52" t="n">
-        <v>0.1474669579364089</v>
+        <v>0.1474669568992967</v>
       </c>
       <c r="C52" t="n">
         <v>24</v>
@@ -1774,13 +1774,13 @@
         <v>0</v>
       </c>
       <c r="E52" t="n">
-        <v>0.2353291683158763</v>
+        <v>0.2353291666666593</v>
       </c>
       <c r="F52" t="n">
-        <v>0.2822488776584991</v>
+        <v>0.2822488780609446</v>
       </c>
       <c r="G52" t="n">
-        <v>-0.4553787556411735</v>
+        <v>-0.4553787597914862</v>
       </c>
       <c r="H52" t="n">
         <v>24</v>
@@ -1791,7 +1791,7 @@
         <v>45808</v>
       </c>
       <c r="B53" t="n">
-        <v>0.3648709334104503</v>
+        <v>0.3648709344318658</v>
       </c>
       <c r="C53" t="n">
         <v>24</v>
@@ -1800,13 +1800,13 @@
         <v>0</v>
       </c>
       <c r="E53" t="n">
-        <v>0.5741583316841125</v>
+        <v>0.5741583333333296</v>
       </c>
       <c r="F53" t="n">
-        <v>1.521677505171866</v>
+        <v>1.521677505186849</v>
       </c>
       <c r="G53" t="n">
-        <v>-0.9860775723761068</v>
+        <v>-0.9860775724152198</v>
       </c>
       <c r="H53" t="n">
         <v>24</v>
@@ -1817,7 +1817,7 @@
         <v>45809</v>
       </c>
       <c r="B54" t="n">
-        <v>14.69931894602372</v>
+        <v>14.6993189441161</v>
       </c>
       <c r="C54" t="n">
         <v>24</v>
@@ -1829,10 +1829,10 @@
         <v>5.355212499999997</v>
       </c>
       <c r="F54" t="n">
-        <v>24.20522383898312</v>
+        <v>24.20522383684717</v>
       </c>
       <c r="G54" t="n">
-        <v>0.8279206123816091</v>
+        <v>0.8279206124119788</v>
       </c>
       <c r="H54" t="n">
         <v>24</v>
@@ -1843,7 +1843,7 @@
         <v>45810</v>
       </c>
       <c r="B55" t="n">
-        <v>0.3852576797566546</v>
+        <v>0.3852576821146208</v>
       </c>
       <c r="C55" t="n">
         <v>24</v>
@@ -1852,13 +1852,13 @@
         <v>0</v>
       </c>
       <c r="E55" t="n">
-        <v>0.1318791658420582</v>
+        <v>0.1318791666666668</v>
       </c>
       <c r="F55" t="n">
-        <v>0.1541634217630745</v>
+        <v>0.1541634224883884</v>
       </c>
       <c r="G55" t="n">
-        <v>-0.6560575478198896</v>
+        <v>-0.6560575634028534</v>
       </c>
       <c r="H55" t="n">
         <v>24</v>
@@ -1869,7 +1869,7 @@
         <v>45811</v>
       </c>
       <c r="B56" t="n">
-        <v>0.2864352994881342</v>
+        <v>0.2864352970238536</v>
       </c>
       <c r="C56" t="n">
         <v>24</v>
@@ -1878,13 +1878,13 @@
         <v>0</v>
       </c>
       <c r="E56" t="n">
-        <v>0.09802500082460923</v>
+        <v>0.09802500000000069</v>
       </c>
       <c r="F56" t="n">
-        <v>0.1176264782487399</v>
+        <v>0.1176264780282624</v>
       </c>
       <c r="G56" t="n">
-        <v>-0.3441339820330307</v>
+        <v>-0.3441339769941782</v>
       </c>
       <c r="H56" t="n">
         <v>24</v>
@@ -1895,7 +1895,7 @@
         <v>45812</v>
       </c>
       <c r="B57" t="n">
-        <v>0.9437236535524406</v>
+        <v>0.9437236534198599</v>
       </c>
       <c r="C57" t="n">
         <v>24</v>
@@ -1907,10 +1907,10 @@
         <v>0.3119999999999997</v>
       </c>
       <c r="F57" t="n">
-        <v>0.7962094394295794</v>
+        <v>0.7962094395739516</v>
       </c>
       <c r="G57" t="n">
-        <v>-0.9674812678813982</v>
+        <v>-0.9674812685949024</v>
       </c>
       <c r="H57" t="n">
         <v>24</v>
@@ -1921,7 +1921,7 @@
         <v>45813</v>
       </c>
       <c r="B58" t="n">
-        <v>0.3023028536796271</v>
+        <v>0.3023028536455489</v>
       </c>
       <c r="C58" t="n">
         <v>24</v>
@@ -1933,10 +1933,10 @@
         <v>0.1032958333333346</v>
       </c>
       <c r="F58" t="n">
-        <v>0.1335270346541159</v>
+        <v>0.1335270353399151</v>
       </c>
       <c r="G58" t="n">
-        <v>-1.343641710476571</v>
+        <v>-1.34364173455061</v>
       </c>
       <c r="H58" t="n">
         <v>24</v>
@@ -1947,7 +1947,7 @@
         <v>45814</v>
       </c>
       <c r="B59" t="n">
-        <v>0.162131879895953</v>
+        <v>0.1621318798731363</v>
       </c>
       <c r="C59" t="n">
         <v>24</v>
@@ -1959,10 +1959,10 @@
         <v>0.05538333333333156</v>
       </c>
       <c r="F59" t="n">
-        <v>0.07293689578693779</v>
+        <v>0.07293689624142949</v>
       </c>
       <c r="G59" t="n">
-        <v>0.1144509020100302</v>
+        <v>0.1144508909737855</v>
       </c>
       <c r="H59" t="n">
         <v>24</v>
@@ -1973,7 +1973,7 @@
         <v>45815</v>
       </c>
       <c r="B60" t="n">
-        <v>0.1966588485676918</v>
+        <v>0.1966588461137087</v>
       </c>
       <c r="C60" t="n">
         <v>24</v>
@@ -1982,13 +1982,13 @@
         <v>0</v>
       </c>
       <c r="E60" t="n">
-        <v>0.0671916674912767</v>
+        <v>0.06719166666666816</v>
       </c>
       <c r="F60" t="n">
-        <v>0.0826547332971492</v>
+        <v>0.08265473368174435</v>
       </c>
       <c r="G60" t="n">
-        <v>0.01063951974397515</v>
+        <v>0.01063951053692247</v>
       </c>
       <c r="H60" t="n">
         <v>24</v>
@@ -1999,7 +1999,7 @@
         <v>45816</v>
       </c>
       <c r="B61" t="n">
-        <v>0.2349807000194508</v>
+        <v>0.2349807024081159</v>
       </c>
       <c r="C61" t="n">
         <v>24</v>
@@ -2008,13 +2008,13 @@
         <v>0</v>
       </c>
       <c r="E61" t="n">
-        <v>0.08010416584205811</v>
+        <v>0.08010416666666664</v>
       </c>
       <c r="F61" t="n">
-        <v>0.09637330546815139</v>
+        <v>0.09637330629726604</v>
       </c>
       <c r="G61" t="n">
-        <v>-1.08129062389067</v>
+        <v>-1.081290659702009</v>
       </c>
       <c r="H61" t="n">
         <v>24</v>
@@ -2025,7 +2025,7 @@
         <v>45817</v>
       </c>
       <c r="B62" t="n">
-        <v>0.1752460173263226</v>
+        <v>0.175246014877185</v>
       </c>
       <c r="C62" t="n">
         <v>24</v>
@@ -2034,13 +2034,13 @@
         <v>0</v>
       </c>
       <c r="E62" t="n">
-        <v>0.05969583415794263</v>
+        <v>0.05969583333333409</v>
       </c>
       <c r="F62" t="n">
-        <v>0.07591743783698734</v>
+        <v>0.07591743870811203</v>
       </c>
       <c r="G62" t="n">
-        <v>-0.8016752382976033</v>
+        <v>-0.8016752796447255</v>
       </c>
       <c r="H62" t="n">
         <v>24</v>
@@ -2051,7 +2051,7 @@
         <v>45818</v>
       </c>
       <c r="B63" t="n">
-        <v>0.2182945216757885</v>
+        <v>0.2182945192210072</v>
       </c>
       <c r="C63" t="n">
         <v>24</v>
@@ -2060,13 +2060,13 @@
         <v>0</v>
       </c>
       <c r="E63" t="n">
-        <v>0.07433750082460892</v>
+        <v>0.07433750000000039</v>
       </c>
       <c r="F63" t="n">
-        <v>0.09406000319285888</v>
+        <v>0.09406000301226157</v>
       </c>
       <c r="G63" t="n">
-        <v>-0.1724543983070506</v>
+        <v>-0.1724543938047731</v>
       </c>
       <c r="H63" t="n">
         <v>24</v>
@@ -2077,7 +2077,7 @@
         <v>45819</v>
       </c>
       <c r="B64" t="n">
-        <v>0.2958373601061243</v>
+        <v>0.2958373649185675</v>
       </c>
       <c r="C64" t="n">
         <v>24</v>
@@ -2086,13 +2086,13 @@
         <v>0</v>
       </c>
       <c r="E64" t="n">
-        <v>0.1006666650174489</v>
+        <v>0.1006666666666659</v>
       </c>
       <c r="F64" t="n">
-        <v>0.1273292824558042</v>
+        <v>0.1273292835852512</v>
       </c>
       <c r="G64" t="n">
-        <v>-0.750414078564914</v>
+        <v>-0.7504141096182573</v>
       </c>
       <c r="H64" t="n">
         <v>24</v>
@@ -2103,7 +2103,7 @@
         <v>45820</v>
       </c>
       <c r="B65" t="n">
-        <v>1.01091563415689</v>
+        <v>1.01091562914195</v>
       </c>
       <c r="C65" t="n">
         <v>24</v>
@@ -2112,13 +2112,13 @@
         <v>0</v>
       </c>
       <c r="E65" t="n">
-        <v>0.3320875016492195</v>
+        <v>0.3320875000000025</v>
       </c>
       <c r="F65" t="n">
-        <v>0.8665925816862676</v>
+        <v>0.8665925816091444</v>
       </c>
       <c r="G65" t="n">
-        <v>-1.179556181416112</v>
+        <v>-1.179556181028169</v>
       </c>
       <c r="H65" t="n">
         <v>24</v>
@@ -2129,7 +2129,7 @@
         <v>45821</v>
       </c>
       <c r="B66" t="n">
-        <v>3.876275024153082</v>
+        <v>3.876275031084569</v>
       </c>
       <c r="C66" t="n">
         <v>24</v>
@@ -2138,13 +2138,13 @@
         <v>0</v>
       </c>
       <c r="E66" t="n">
-        <v>1.190958330859506</v>
+        <v>1.190958333333331</v>
       </c>
       <c r="F66" t="n">
-        <v>2.11916425895623</v>
+        <v>2.119164259010298</v>
       </c>
       <c r="G66" t="n">
-        <v>-0.5468941058967924</v>
+        <v>-0.5468941059757271</v>
       </c>
       <c r="H66" t="n">
         <v>24</v>
@@ -2155,7 +2155,7 @@
         <v>45822</v>
       </c>
       <c r="B67" t="n">
-        <v>0.3196557036840145</v>
+        <v>0.3196557060676633</v>
       </c>
       <c r="C67" t="n">
         <v>24</v>
@@ -2164,13 +2164,13 @@
         <v>0</v>
       </c>
       <c r="E67" t="n">
-        <v>0.108558332508724</v>
+        <v>0.1085583333333326</v>
       </c>
       <c r="F67" t="n">
-        <v>0.1209998812055979</v>
+        <v>0.1209998820591704</v>
       </c>
       <c r="G67" t="n">
-        <v>-0.8905511010501999</v>
+        <v>-0.8905511277233238</v>
       </c>
       <c r="H67" t="n">
         <v>24</v>
@@ -2181,7 +2181,7 @@
         <v>45823</v>
       </c>
       <c r="B68" t="n">
-        <v>0.2336150225849331</v>
+        <v>0.2336150201176904</v>
       </c>
       <c r="C68" t="n">
         <v>24</v>
@@ -2190,13 +2190,13 @@
         <v>0</v>
       </c>
       <c r="E68" t="n">
-        <v>0.07930416749127674</v>
+        <v>0.07930416666666822</v>
       </c>
       <c r="F68" t="n">
-        <v>0.09912500080295997</v>
+        <v>0.09912500105086196</v>
       </c>
       <c r="G68" t="n">
-        <v>-0.345690333924991</v>
+        <v>-0.3456903406558725</v>
       </c>
       <c r="H68" t="n">
         <v>24</v>
@@ -2207,7 +2207,7 @@
         <v>45824</v>
       </c>
       <c r="B69" t="n">
-        <v>2.294564858137942</v>
+        <v>2.29456485779949</v>
       </c>
       <c r="C69" t="n">
         <v>24</v>
@@ -2219,10 +2219,10 @@
         <v>0.7451208333333327</v>
       </c>
       <c r="F69" t="n">
-        <v>1.394179214587187</v>
+        <v>1.394179214627732</v>
       </c>
       <c r="G69" t="n">
-        <v>-1.261256163393129</v>
+        <v>-1.26125616352465</v>
       </c>
       <c r="H69" t="n">
         <v>24</v>
@@ -2233,7 +2233,7 @@
         <v>45825</v>
       </c>
       <c r="B70" t="n">
-        <v>0.8834975731149993</v>
+        <v>0.8834975778618159</v>
       </c>
       <c r="C70" t="n">
         <v>24</v>
@@ -2242,13 +2242,13 @@
         <v>0</v>
       </c>
       <c r="E70" t="n">
-        <v>0.2881833316841146</v>
+        <v>0.2881833333333317</v>
       </c>
       <c r="F70" t="n">
-        <v>0.7850811422324497</v>
+        <v>0.7850811423031382</v>
       </c>
       <c r="G70" t="n">
-        <v>-0.9631268287686925</v>
+        <v>-0.9631268291222108</v>
       </c>
       <c r="H70" t="n">
         <v>24</v>
@@ -2259,7 +2259,7 @@
         <v>45826</v>
       </c>
       <c r="B71" t="n">
-        <v>0.2340610454837405</v>
+        <v>0.2340610503120596</v>
       </c>
       <c r="C71" t="n">
         <v>24</v>
@@ -2268,13 +2268,13 @@
         <v>0</v>
       </c>
       <c r="E71" t="n">
-        <v>0.07923124835078148</v>
+        <v>0.07923124999999853</v>
       </c>
       <c r="F71" t="n">
-        <v>0.101522052842663</v>
+        <v>0.1015220537412093</v>
       </c>
       <c r="G71" t="n">
-        <v>-0.6430265125935879</v>
+        <v>-0.6430265416776229</v>
       </c>
       <c r="H71" t="n">
         <v>24</v>
@@ -2285,7 +2285,7 @@
         <v>45827</v>
       </c>
       <c r="B72" t="n">
-        <v>1.596707351668318</v>
+        <v>1.596707346548572</v>
       </c>
       <c r="C72" t="n">
         <v>24</v>
@@ -2294,13 +2294,13 @@
         <v>0</v>
       </c>
       <c r="E72" t="n">
-        <v>0.5211395849825516</v>
+        <v>0.5211395833333347</v>
       </c>
       <c r="F72" t="n">
-        <v>1.132338517052953</v>
+        <v>1.132338517138684</v>
       </c>
       <c r="G72" t="n">
-        <v>-1.248442040500756</v>
+        <v>-1.248442040841224</v>
       </c>
       <c r="H72" t="n">
         <v>24</v>
@@ -2311,7 +2311,7 @@
         <v>45828</v>
       </c>
       <c r="B73" t="n">
-        <v>1.710378469844584</v>
+        <v>1.710378471903394</v>
       </c>
       <c r="C73" t="n">
         <v>24</v>
@@ -2320,13 +2320,13 @@
         <v>0</v>
       </c>
       <c r="E73" t="n">
-        <v>0.559304165842058</v>
+        <v>0.5593041666666666</v>
       </c>
       <c r="F73" t="n">
-        <v>1.189016665810993</v>
+        <v>1.189016665848998</v>
       </c>
       <c r="G73" t="n">
-        <v>-0.5636067004657308</v>
+        <v>-0.5636067005656868</v>
       </c>
       <c r="H73" t="n">
         <v>24</v>
@@ -2337,7 +2337,7 @@
         <v>45829</v>
       </c>
       <c r="B74" t="n">
-        <v>0.1485001254629494</v>
+        <v>0.1485001278747083</v>
       </c>
       <c r="C74" t="n">
         <v>24</v>
@@ -2346,13 +2346,13 @@
         <v>0</v>
       </c>
       <c r="E74" t="n">
-        <v>0.05044583250872344</v>
+        <v>0.05044583333333197</v>
       </c>
       <c r="F74" t="n">
-        <v>0.06239123099594261</v>
+        <v>0.06239123202288234</v>
       </c>
       <c r="G74" t="n">
-        <v>-0.522840949915208</v>
+        <v>-0.5228410000461592</v>
       </c>
       <c r="H74" t="n">
         <v>24</v>
@@ -2363,7 +2363,7 @@
         <v>45830</v>
       </c>
       <c r="B75" t="n">
-        <v>1.172357287202175</v>
+        <v>1.172357291878556</v>
       </c>
       <c r="C75" t="n">
         <v>24</v>
@@ -2372,13 +2372,13 @@
         <v>0</v>
       </c>
       <c r="E75" t="n">
-        <v>0.3865374983507817</v>
+        <v>0.3865374999999987</v>
       </c>
       <c r="F75" t="n">
-        <v>0.89184992886271</v>
+        <v>0.8918499289865606</v>
       </c>
       <c r="G75" t="n">
-        <v>-1.194290700806224</v>
+        <v>-1.194290701415663</v>
       </c>
       <c r="H75" t="n">
         <v>24</v>
@@ -2389,7 +2389,7 @@
         <v>45831</v>
       </c>
       <c r="B76" t="n">
-        <v>1.652285671282684</v>
+        <v>1.652285673462173</v>
       </c>
       <c r="C76" t="n">
         <v>24</v>
@@ -2398,13 +2398,13 @@
         <v>0</v>
       </c>
       <c r="E76" t="n">
-        <v>0.5402999991753908</v>
+        <v>0.5402999999999993</v>
       </c>
       <c r="F76" t="n">
-        <v>1.160464876226755</v>
+        <v>1.160464876317532</v>
       </c>
       <c r="G76" t="n">
-        <v>-1.191992508358721</v>
+        <v>-1.191992508701657</v>
       </c>
       <c r="H76" t="n">
         <v>24</v>
@@ -2415,7 +2415,7 @@
         <v>45832</v>
       </c>
       <c r="B77" t="n">
-        <v>1.656238773526162</v>
+        <v>1.656238778230692</v>
       </c>
       <c r="C77" t="n">
         <v>24</v>
@@ -2424,13 +2424,13 @@
         <v>0</v>
       </c>
       <c r="E77" t="n">
-        <v>0.5410499983507817</v>
+        <v>0.5410499999999988</v>
       </c>
       <c r="F77" t="n">
-        <v>1.163689308811113</v>
+        <v>1.16368930883634</v>
       </c>
       <c r="G77" t="n">
-        <v>-0.4939884313026335</v>
+        <v>-0.4939884313674072</v>
       </c>
       <c r="H77" t="n">
         <v>24</v>
@@ -2441,7 +2441,7 @@
         <v>45833</v>
       </c>
       <c r="B78" t="n">
-        <v>0.2323824145484092</v>
+        <v>0.2323824217882976</v>
       </c>
       <c r="C78" t="n">
         <v>24</v>
@@ -2450,13 +2450,13 @@
         <v>0</v>
       </c>
       <c r="E78" t="n">
-        <v>0.07909583085950622</v>
+        <v>0.07909583333333181</v>
       </c>
       <c r="F78" t="n">
-        <v>0.1043619895631973</v>
+        <v>0.1043619902071631</v>
       </c>
       <c r="G78" t="n">
-        <v>-0.702746052342835</v>
+        <v>-0.7027460733564268</v>
       </c>
       <c r="H78" t="n">
         <v>24</v>
@@ -2467,7 +2467,7 @@
         <v>45834</v>
       </c>
       <c r="B79" t="n">
-        <v>0.1966299651788086</v>
+        <v>0.1966299675806902</v>
       </c>
       <c r="C79" t="n">
         <v>24</v>
@@ -2476,13 +2476,13 @@
         <v>0</v>
       </c>
       <c r="E79" t="n">
-        <v>0.06672083250872578</v>
+        <v>0.0667208333333343</v>
       </c>
       <c r="F79" t="n">
-        <v>0.07841901320912571</v>
+        <v>0.07841901342574266</v>
       </c>
       <c r="G79" t="n">
-        <v>0.04287163294723906</v>
+        <v>0.04287162765948516</v>
       </c>
       <c r="H79" t="n">
         <v>24</v>
@@ -2493,7 +2493,7 @@
         <v>45835</v>
       </c>
       <c r="B80" t="n">
-        <v>0.9222002878326299</v>
+        <v>0.9222002925514107</v>
       </c>
       <c r="C80" t="n">
         <v>24</v>
@@ -2502,13 +2502,13 @@
         <v>0</v>
       </c>
       <c r="E80" t="n">
-        <v>0.3024499983507812</v>
+        <v>0.3024499999999983</v>
       </c>
       <c r="F80" t="n">
-        <v>0.8436169424754546</v>
+        <v>0.8436169425949989</v>
       </c>
       <c r="G80" t="n">
-        <v>-1.083951412241087</v>
+        <v>-1.083951412831698</v>
       </c>
       <c r="H80" t="n">
         <v>24</v>
@@ -2519,7 +2519,7 @@
         <v>45836</v>
       </c>
       <c r="B81" t="n">
-        <v>3.058455213802779</v>
+        <v>3.058455221489063</v>
       </c>
       <c r="C81" t="n">
         <v>24</v>
@@ -2528,13 +2528,13 @@
         <v>0</v>
       </c>
       <c r="E81" t="n">
-        <v>1.970287497526171</v>
+        <v>1.970287499999997</v>
       </c>
       <c r="F81" t="n">
-        <v>6.416656393866447</v>
+        <v>6.416656396701738</v>
       </c>
       <c r="G81" t="n">
-        <v>0.9020741264817342</v>
+        <v>0.9020741263951944</v>
       </c>
       <c r="H81" t="n">
         <v>24</v>
@@ -2545,7 +2545,7 @@
         <v>45837</v>
       </c>
       <c r="B82" t="n">
-        <v>2.882585243071706</v>
+        <v>2.882585243501183</v>
       </c>
       <c r="C82" t="n">
         <v>24</v>
@@ -2554,13 +2554,13 @@
         <v>0</v>
       </c>
       <c r="E82" t="n">
-        <v>3.627045832508724</v>
+        <v>3.627045833333333</v>
       </c>
       <c r="F82" t="n">
-        <v>9.556372088844007</v>
+        <v>9.556372092352825</v>
       </c>
       <c r="G82" t="n">
-        <v>0.9315363098534337</v>
+        <v>0.931536309803158</v>
       </c>
       <c r="H82" t="n">
         <v>24</v>
@@ -2571,7 +2571,7 @@
         <v>45838</v>
       </c>
       <c r="B83" t="n">
-        <v>0.7820534878860157</v>
+        <v>0.7820534875896092</v>
       </c>
       <c r="C83" t="n">
         <v>23</v>
@@ -2580,13 +2580,13 @@
         <v>0</v>
       </c>
       <c r="E83" t="n">
-        <v>1.222123913473715</v>
+        <v>1.222123913043484</v>
       </c>
       <c r="F83" t="n">
-        <v>2.238401836430449</v>
+        <v>2.238401836156471</v>
       </c>
       <c r="G83" t="n">
-        <v>-1.703455410699643</v>
+        <v>-1.703455410037843</v>
       </c>
       <c r="H83" t="n">
         <v>23</v>
